--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -503,10 +503,10 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="21.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -696,7 +696,7 @@
         <v>-0.3178304128441319</v>
       </c>
       <c r="L5">
-        <v>0.3140610795011265</v>
+        <v>0.3140610795011266</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -833,22 +833,22 @@
         <v>92</v>
       </c>
       <c r="G9">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>-0.2232481170885827</v>
+        <v>-0.2266499931585039</v>
       </c>
       <c r="J9">
-        <v>0.001636069376151588</v>
+        <v>0.001388944087542739</v>
       </c>
       <c r="K9">
-        <v>-0.3234519555354279</v>
+        <v>-0.3292121926341289</v>
       </c>
       <c r="L9">
-        <v>0.001028681640569814</v>
+        <v>0.0008243882531155807</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -871,22 +871,22 @@
         <v>46</v>
       </c>
       <c r="G10">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.05768310136706124</v>
+        <v>0.01866777293784236</v>
       </c>
       <c r="J10">
-        <v>0.5808166089173682</v>
+        <v>0.8583574614657677</v>
       </c>
       <c r="K10">
-        <v>-0.06873895440322977</v>
+        <v>0.02926774595311432</v>
       </c>
       <c r="L10">
-        <v>0.635267646345926</v>
+        <v>0.8401020874019567</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -909,22 +909,22 @@
         <v>46</v>
       </c>
       <c r="G11">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.03854494781179903</v>
+        <v>0.03525306566614442</v>
       </c>
       <c r="J11">
-        <v>0.6995394491817443</v>
+        <v>0.7244530391680126</v>
       </c>
       <c r="K11">
-        <v>-0.04832503745113209</v>
+        <v>0.03962642574794883</v>
       </c>
       <c r="L11">
-        <v>0.7389368221688255</v>
+        <v>0.7846830695577185</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -947,22 +947,22 @@
         <v>46</v>
       </c>
       <c r="G12">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1156617751198898</v>
+        <v>0.1975428742000058</v>
       </c>
       <c r="J12">
-        <v>0.2438312496350385</v>
+        <v>0.04682237144660668</v>
       </c>
       <c r="K12">
-        <v>0.1718948469712283</v>
+        <v>0.2832674538277786</v>
       </c>
       <c r="L12">
-        <v>0.2326162766495191</v>
+        <v>0.04622012001137949</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -985,22 +985,22 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-0.3373495424699933</v>
+        <v>-0.5284193913361779</v>
       </c>
       <c r="J13">
-        <v>0.2074202127647988</v>
+        <v>0.05682819683984795</v>
       </c>
       <c r="K13">
-        <v>-0.4296689244236597</v>
+        <v>-0.6292532049656926</v>
       </c>
       <c r="L13">
-        <v>0.215243543278886</v>
+        <v>0.05126402824042627</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1023,22 +1023,22 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-0.1816497536376887</v>
+        <v>-0.4662524041201569</v>
       </c>
       <c r="J14">
-        <v>0.4972433060612282</v>
+        <v>0.09284922807157968</v>
       </c>
       <c r="K14">
-        <v>-0.2669155439601523</v>
+        <v>-0.5618332187193684</v>
       </c>
       <c r="L14">
-        <v>0.4559719917038285</v>
+        <v>0.090982576216914</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1061,22 +1061,22 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-0.0524863881081478</v>
+        <v>-0.3143473067309657</v>
       </c>
       <c r="J15">
-        <v>0.8456867367859529</v>
+        <v>0.2610207247026572</v>
       </c>
       <c r="K15">
-        <v>-0.06856450678985078</v>
+        <v>-0.3719387243003159</v>
       </c>
       <c r="L15">
-        <v>0.8507182473580949</v>
+        <v>0.2899037448075479</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1099,22 +1099,22 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.7525489793561388</v>
+        <v>-0.5905863785521988</v>
       </c>
       <c r="J16">
-        <v>0.004918698145511134</v>
+        <v>0.03327875704510121</v>
       </c>
       <c r="K16">
-        <v>-0.8788682545029405</v>
+        <v>-0.6741998624632421</v>
       </c>
       <c r="L16">
-        <v>0.000811787483996615</v>
+        <v>0.03251559932021606</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1137,22 +1137,22 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.1816497536376887</v>
+        <v>0.03108349360801046</v>
       </c>
       <c r="J17">
-        <v>0.4972433060612282</v>
+        <v>0.9107940274245708</v>
       </c>
       <c r="K17">
-        <v>-0.260405408741612</v>
+        <v>0.02247332874877474</v>
       </c>
       <c r="L17">
-        <v>0.4674445466605421</v>
+        <v>0.9508644143273767</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1175,22 +1175,22 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>0.4411494016915297</v>
+        <v>0.404085416904136</v>
       </c>
       <c r="J18">
-        <v>0.09923045565594253</v>
+        <v>0.1452595077432854</v>
       </c>
       <c r="K18">
-        <v>0.5143006822646836</v>
+        <v>0.4944132324730443</v>
       </c>
       <c r="L18">
-        <v>0.1282920587230653</v>
+        <v>0.1463267160789159</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1213,22 +1213,22 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>0.4198911048651824</v>
+        <v>0.4400862294233521</v>
       </c>
       <c r="J19">
-        <v>0.1194709867717007</v>
+        <v>0.1155858306979473</v>
       </c>
       <c r="K19">
-        <v>0.5060713596393749</v>
+        <v>0.5297309103671165</v>
       </c>
       <c r="L19">
-        <v>0.1355782583455031</v>
+        <v>0.1152952650343875</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1251,22 +1251,22 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-0.3892494720807615</v>
+        <v>-0.404085416904136</v>
       </c>
       <c r="J20">
-        <v>0.1457680056362324</v>
+        <v>0.1452595077432854</v>
       </c>
       <c r="K20">
-        <v>-0.5077905470461433</v>
+        <v>-0.4494665749754947</v>
       </c>
       <c r="L20">
-        <v>0.1340355823255553</v>
+        <v>0.1925017251163437</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1289,22 +1289,22 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.3373495424699933</v>
+        <v>-0.2175844552560732</v>
       </c>
       <c r="J21">
-        <v>0.2074202127647988</v>
+        <v>0.4328879340133424</v>
       </c>
       <c r="K21">
-        <v>-0.4687297357349016</v>
+        <v>-0.3146266024828463</v>
       </c>
       <c r="L21">
-        <v>0.1717865787289185</v>
+        <v>0.3759325783116143</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1327,22 +1327,22 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.0778498944161523</v>
+        <v>-0.2175844552560732</v>
       </c>
       <c r="J22">
-        <v>0.7711058640185235</v>
+        <v>0.4328879340133424</v>
       </c>
       <c r="K22">
-        <v>0.09765202827810447</v>
+        <v>-0.2696799449852968</v>
       </c>
       <c r="L22">
-        <v>0.788411563708648</v>
+        <v>0.4511390079856625</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1365,22 +1365,22 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.1297498240269205</v>
+        <v>-0.1554174680400523</v>
       </c>
       <c r="J23">
-        <v>0.6277606629910362</v>
+        <v>0.5753530764008791</v>
       </c>
       <c r="K23">
-        <v>0.2083243269932896</v>
+        <v>-0.1573133012414231</v>
       </c>
       <c r="L23">
-        <v>0.5635582121900502</v>
+        <v>0.6642676178335104</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1403,22 +1403,22 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.2335496832484569</v>
+        <v>-0.03108349360801046</v>
       </c>
       <c r="J24">
-        <v>0.3827797056047885</v>
+        <v>0.9107940274245708</v>
       </c>
       <c r="K24">
-        <v>-0.3320168961455552</v>
+        <v>-0.04494665749754947</v>
       </c>
       <c r="L24">
-        <v>0.3486190102393061</v>
+        <v>0.9018775739844269</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1438,25 +1438,25 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>16</v>
       </c>
       <c r="I25">
-        <v>-0.1807753815155468</v>
+        <v>-0.3208833147655317</v>
       </c>
       <c r="J25">
-        <v>0.3541954904764164</v>
+        <v>0.1310095881916458</v>
       </c>
       <c r="K25">
-        <v>-0.2576049186596542</v>
+        <v>-0.3615507630310936</v>
       </c>
       <c r="L25">
-        <v>0.3354345184285685</v>
+        <v>0.1688293942897778</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1476,25 +1476,25 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H26">
         <v>16</v>
       </c>
       <c r="I26">
-        <v>-0.1807753815155468</v>
+        <v>-0.1544993737759967</v>
       </c>
       <c r="J26">
-        <v>0.3541954904764164</v>
+        <v>0.4671641537476017</v>
       </c>
       <c r="K26">
-        <v>-0.2666436877354316</v>
+        <v>-0.1717366124397695</v>
       </c>
       <c r="L26">
-        <v>0.3181414648703181</v>
+        <v>0.5247923002825454</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1514,25 +1514,25 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H27">
         <v>16</v>
       </c>
       <c r="I27">
-        <v>0.3539900381483285</v>
+        <v>0.3341631412724104</v>
       </c>
       <c r="J27">
-        <v>0.07056136851892029</v>
+        <v>0.1170517823729769</v>
       </c>
       <c r="K27">
-        <v>0.4341802833034056</v>
+        <v>0.3934758817437114</v>
       </c>
       <c r="L27">
-        <v>0.09288178063084394</v>
+        <v>0.1315976135653158</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1552,25 +1552,25 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>16</v>
       </c>
       <c r="I28">
-        <v>-0.1647705109143269</v>
+        <v>-0.4694027940381773</v>
       </c>
       <c r="J28">
-        <v>0.4027546538976249</v>
+        <v>0.0286729854548637</v>
       </c>
       <c r="K28">
-        <v>-0.2493004677260264</v>
+        <v>-0.5439282932204211</v>
       </c>
       <c r="L28">
-        <v>0.3517858440384553</v>
+        <v>0.0294039628831014</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1590,25 +1590,25 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>16</v>
       </c>
       <c r="I29">
-        <v>-0.1265427670608828</v>
+        <v>0.05942283606769105</v>
       </c>
       <c r="J29">
-        <v>0.5166373798159882</v>
+        <v>0.77974282876954</v>
       </c>
       <c r="K29">
-        <v>-0.1491396897503261</v>
+        <v>0.05423261445466403</v>
       </c>
       <c r="L29">
-        <v>0.5814513259975999</v>
+        <v>0.841887936826351</v>
       </c>
     </row>
   </sheetData>
@@ -1946,25 +1946,25 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G10">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.2741939043543897</v>
+        <v>-0.1513701890060563</v>
       </c>
       <c r="J10">
-        <v>0.01523742906785629</v>
+        <v>0.1849849928400071</v>
       </c>
       <c r="K10">
-        <v>-0.3438060590640694</v>
+        <v>-0.1909099024833014</v>
       </c>
       <c r="L10">
-        <v>0.0145005762354219</v>
+        <v>0.1841630933746127</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1984,25 +1984,25 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G11">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.2885159533670518</v>
+        <v>-0.1912266713473635</v>
       </c>
       <c r="J11">
-        <v>0.007534224862278689</v>
+        <v>0.07966527054092901</v>
       </c>
       <c r="K11">
-        <v>-0.3916527812158478</v>
+        <v>-0.2629384536176831</v>
       </c>
       <c r="L11">
-        <v>0.00491305256761129</v>
+        <v>0.06506084897945322</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2022,25 +2022,25 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G12">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1527404930393114</v>
+        <v>0.2310064793132821</v>
       </c>
       <c r="J12">
-        <v>0.1545006958890939</v>
+        <v>0.03309841101323721</v>
       </c>
       <c r="K12">
-        <v>0.1874148805812322</v>
+        <v>0.2844439628835274</v>
       </c>
       <c r="L12">
-        <v>0.192476549579598</v>
+        <v>0.04528302631069108</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2060,25 +2060,25 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>0.3651483716701108</v>
+        <v>0.07453559924999299</v>
       </c>
       <c r="J13">
-        <v>0.2008251226951454</v>
+        <v>0.794002680192762</v>
       </c>
       <c r="K13">
-        <v>0.4264014327112208</v>
+        <v>0.08703882797784893</v>
       </c>
       <c r="L13">
-        <v>0.2191383605228726</v>
+        <v>0.8110384240587123</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2098,25 +2098,25 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>0.7302967433402215</v>
+        <v>0.3726779962499649</v>
       </c>
       <c r="J14">
-        <v>0.01051524593585891</v>
+        <v>0.191694602051888</v>
       </c>
       <c r="K14">
-        <v>0.8528028654224417</v>
+        <v>0.4351941398892446</v>
       </c>
       <c r="L14">
-        <v>0.001712874149321468</v>
+        <v>0.2087486300875882</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2136,25 +2136,25 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>0.7385489458759965</v>
+        <v>0.3768891807222045</v>
       </c>
       <c r="J15">
-        <v>0.01028204822194895</v>
+        <v>0.1903458092612167</v>
       </c>
       <c r="K15">
-        <v>0.8553989227683017</v>
+        <v>0.4365189348559864</v>
       </c>
       <c r="L15">
-        <v>0.001600453316805279</v>
+        <v>0.2072083540976897</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2174,25 +2174,25 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.1217161238900369</v>
+        <v>0.149071198499986</v>
       </c>
       <c r="J16">
-        <v>0.6698153575994166</v>
+        <v>0.6015081344405899</v>
       </c>
       <c r="K16">
-        <v>-0.1421338109037403</v>
+        <v>0.1740776559556979</v>
       </c>
       <c r="L16">
-        <v>0.6952876854012655</v>
+        <v>0.6305360755569764</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -2212,25 +2212,25 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.5477225575051662</v>
+        <v>-0.223606797749979</v>
       </c>
       <c r="J17">
-        <v>0.05500883362926572</v>
+        <v>0.4334219309560737</v>
       </c>
       <c r="K17">
-        <v>-0.6396021490668313</v>
+        <v>-0.2611164839335468</v>
       </c>
       <c r="L17">
-        <v>0.04643461767158175</v>
+        <v>0.4661852835040308</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -2250,25 +2250,25 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-0.3651483716701108</v>
+        <v>-0.4472135954999579</v>
       </c>
       <c r="J18">
-        <v>0.2008251226951454</v>
+        <v>0.117185087198138</v>
       </c>
       <c r="K18">
-        <v>-0.4264014327112208</v>
+        <v>-0.5222329678670935</v>
       </c>
       <c r="L18">
-        <v>0.2191383605228726</v>
+        <v>0.1215029188171132</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2288,25 +2288,25 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-0.3077287274483319</v>
+        <v>-0.3015113445777636</v>
       </c>
       <c r="J19">
-        <v>0.2849576406684299</v>
+        <v>0.2948019919337048</v>
       </c>
       <c r="K19">
-        <v>-0.3564162178201257</v>
+        <v>-0.3492151478847891</v>
       </c>
       <c r="L19">
-        <v>0.312061132326838</v>
+        <v>0.3226327672991101</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2326,25 +2326,25 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>0.3042903097250923</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J20">
-        <v>0.2864220227778588</v>
+        <v>0.117185087198138</v>
       </c>
       <c r="K20">
-        <v>0.3553345272593507</v>
+        <v>0.5222329678670935</v>
       </c>
       <c r="L20">
-        <v>0.3136373640754537</v>
+        <v>0.1215029188171132</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2364,25 +2364,25 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.3651483716701108</v>
+        <v>-0.223606797749979</v>
       </c>
       <c r="J21">
-        <v>0.2008251226951454</v>
+        <v>0.4334219309560737</v>
       </c>
       <c r="K21">
-        <v>-0.4264014327112208</v>
+        <v>-0.2611164839335468</v>
       </c>
       <c r="L21">
-        <v>0.2191383605228726</v>
+        <v>0.4661852835040308</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2402,25 +2402,25 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.3042903097250923</v>
+        <v>-0.223606797749979</v>
       </c>
       <c r="J22">
-        <v>0.2864220227778588</v>
+        <v>0.4334219309560737</v>
       </c>
       <c r="K22">
-        <v>0.3553345272593507</v>
+        <v>-0.2611164839335468</v>
       </c>
       <c r="L22">
-        <v>0.3136373640754537</v>
+        <v>0.4661852835040308</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2440,25 +2440,25 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.3651483716701108</v>
+        <v>-0.149071198499986</v>
       </c>
       <c r="J23">
-        <v>0.2008251226951454</v>
+        <v>0.6015081344405899</v>
       </c>
       <c r="K23">
-        <v>0.4264014327112208</v>
+        <v>-0.1740776559556979</v>
       </c>
       <c r="L23">
-        <v>0.2191383605228726</v>
+        <v>0.6305360755569764</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2478,25 +2478,25 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.4260064336151292</v>
+        <v>-0.07453559924999299</v>
       </c>
       <c r="J24">
-        <v>0.1355930012663022</v>
+        <v>0.794002680192762</v>
       </c>
       <c r="K24">
-        <v>-0.497468338163091</v>
+        <v>-0.08703882797784893</v>
       </c>
       <c r="L24">
-        <v>0.1434614655950857</v>
+        <v>0.8110384240587123</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2707,9 +2707,9 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3075,22 +3075,22 @@
         <v>40</v>
       </c>
       <c r="G10">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>0.03324642499485375</v>
+        <v>0.08712167584961492</v>
       </c>
       <c r="J10">
-        <v>0.7524695495544889</v>
+        <v>0.4083766752312095</v>
       </c>
       <c r="K10">
-        <v>0.05369692827151148</v>
+        <v>0.1227687641955272</v>
       </c>
       <c r="L10">
-        <v>0.7111154281850389</v>
+        <v>0.3956759834281137</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3113,22 +3113,22 @@
         <v>40</v>
       </c>
       <c r="G11">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>0.02630142666529713</v>
+        <v>0.07462967377124524</v>
       </c>
       <c r="J11">
-        <v>0.7941029996140164</v>
+        <v>0.4588124610579571</v>
       </c>
       <c r="K11">
-        <v>0.0345247475921612</v>
+        <v>0.09255821810809323</v>
       </c>
       <c r="L11">
-        <v>0.8118632018166435</v>
+        <v>0.5226237277667096</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3151,22 +3151,22 @@
         <v>40</v>
       </c>
       <c r="G12">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.02696081483975262</v>
+        <v>0.0648462728029752</v>
       </c>
       <c r="J12">
-        <v>0.7877495099042957</v>
+        <v>0.5171200381290717</v>
       </c>
       <c r="K12">
-        <v>0.03904490288887924</v>
+        <v>0.08638478532010939</v>
       </c>
       <c r="L12">
-        <v>0.7877690834629696</v>
+        <v>0.5508414269428876</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3189,22 +3189,22 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-0.4787549991450212</v>
+        <v>-0.6366820122120065</v>
       </c>
       <c r="J13">
-        <v>0.07217560549492458</v>
+        <v>0.01869720062275651</v>
       </c>
       <c r="K13">
-        <v>-0.6292853089020909</v>
+        <v>-0.8019532181238483</v>
       </c>
       <c r="L13">
-        <v>0.05124855216842294</v>
+        <v>0.005259237421010194</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3227,22 +3227,22 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-0.2267786838055363</v>
+        <v>-0.4705910525045265</v>
       </c>
       <c r="J14">
-        <v>0.3943870594034554</v>
+        <v>0.08219753762575091</v>
       </c>
       <c r="K14">
-        <v>-0.2860387767736777</v>
+        <v>-0.5414897797588377</v>
       </c>
       <c r="L14">
-        <v>0.4230203924441357</v>
+        <v>0.1059666504898876</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3265,22 +3265,22 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-0.1019294382875251</v>
+        <v>-0.3359355065735126</v>
       </c>
       <c r="J15">
-        <v>0.7040542681897126</v>
+        <v>0.218311625181403</v>
       </c>
       <c r="K15">
-        <v>-0.0765092055676006</v>
+        <v>-0.3506334920077187</v>
       </c>
       <c r="L15">
-        <v>0.8336123677972922</v>
+        <v>0.3205360031284263</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3303,22 +3303,22 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.579545525280815</v>
+        <v>-0.3598637460328732</v>
       </c>
       <c r="J16">
-        <v>0.02951512807757192</v>
+        <v>0.1838095557893692</v>
       </c>
       <c r="K16">
-        <v>-0.7119187333033755</v>
+        <v>-0.4592381676435712</v>
       </c>
       <c r="L16">
-        <v>0.02091481468718881</v>
+        <v>0.1818195500051732</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -3341,22 +3341,22 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.1259881576697424</v>
+        <v>0.08304547985373997</v>
       </c>
       <c r="J17">
-        <v>0.6360988735986226</v>
+        <v>0.7590571299004958</v>
       </c>
       <c r="K17">
-        <v>-0.1906925178491184</v>
+        <v>0.08910591312487204</v>
       </c>
       <c r="L17">
-        <v>0.5977007516614028</v>
+        <v>0.8066210879575378</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -3379,22 +3379,22 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>0.579545525280815</v>
+        <v>0.5259547057403532</v>
       </c>
       <c r="J18">
-        <v>0.02951512807757192</v>
+        <v>0.05206997227535645</v>
       </c>
       <c r="K18">
-        <v>0.7437008196115621</v>
+        <v>0.7128473049989763</v>
       </c>
       <c r="L18">
-        <v>0.01366958411527145</v>
+        <v>0.02067214786469852</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3417,22 +3417,22 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>0.560611910581388</v>
+        <v>0.5598925109558542</v>
       </c>
       <c r="J19">
-        <v>0.0366903087793031</v>
+        <v>0.04019719781553128</v>
       </c>
       <c r="K19">
-        <v>0.7172738021962557</v>
+        <v>0.7253300668002809</v>
       </c>
       <c r="L19">
-        <v>0.01954204435368506</v>
+        <v>0.01759621904480188</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3455,22 +3455,22 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-0.4787549991450212</v>
+        <v>-0.4705910525045265</v>
       </c>
       <c r="J20">
-        <v>0.07217560549492458</v>
+        <v>0.08219753762575091</v>
       </c>
       <c r="K20">
-        <v>-0.6419981434253655</v>
+        <v>-0.5689069837972599</v>
       </c>
       <c r="L20">
-        <v>0.04536158917864154</v>
+        <v>0.08610936073892451</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -3493,22 +3493,22 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.2771739468734333</v>
+        <v>-0.1384091330895666</v>
       </c>
       <c r="J21">
-        <v>0.2978975979923409</v>
+        <v>0.6092119761915052</v>
       </c>
       <c r="K21">
-        <v>-0.3750286184365996</v>
+        <v>-0.1987747292785607</v>
       </c>
       <c r="L21">
-        <v>0.2855969029688312</v>
+        <v>0.5819571528087297</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -3531,22 +3531,22 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.1259881576697424</v>
+        <v>-0.1384091330895666</v>
       </c>
       <c r="J22">
-        <v>0.6360988735986226</v>
+        <v>0.6092119761915052</v>
       </c>
       <c r="K22">
-        <v>0.1461975970176575</v>
+        <v>-0.1919204282689551</v>
       </c>
       <c r="L22">
-        <v>0.6869410188538527</v>
+        <v>0.595298950736874</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -3569,22 +3569,22 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.1259881576697424</v>
+        <v>-0.1384091330895666</v>
       </c>
       <c r="J23">
-        <v>0.6360988735986226</v>
+        <v>0.6092119761915052</v>
       </c>
       <c r="K23">
-        <v>0.2161181868956676</v>
+        <v>-0.1302317191825053</v>
       </c>
       <c r="L23">
-        <v>0.5487107060733141</v>
+        <v>0.7199008272052645</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -3607,22 +3607,22 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.2267786838055363</v>
+        <v>-0.02768182661791332</v>
       </c>
       <c r="J24">
-        <v>0.3943870594034554</v>
+        <v>0.9185663957730847</v>
       </c>
       <c r="K24">
-        <v>-0.3114644458202268</v>
+        <v>-0.02741720403842217</v>
       </c>
       <c r="L24">
-        <v>0.3810089567050594</v>
+        <v>0.9400699293286143</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -4196,7 +4196,7 @@
         <v>0.2933526131391836</v>
       </c>
       <c r="L12">
-        <v>0.03867934687031337</v>
+        <v>0.03867934687031339</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -4988,7 +4988,7 @@
         <v>-0.5561107852980067</v>
       </c>
       <c r="L7">
-        <v>0.0604349562009266</v>
+        <v>0.06043495620092659</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -5046,25 +5046,25 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>-0.1777071888309779</v>
+        <v>-0.1869261787362204</v>
       </c>
       <c r="J9">
-        <v>0.02109743444634812</v>
+        <v>0.01502626043323942</v>
       </c>
       <c r="K9">
-        <v>-0.2338626244994551</v>
+        <v>-0.2423346744391451</v>
       </c>
       <c r="L9">
-        <v>0.01919115836424928</v>
+        <v>0.01513196719297787</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -5084,25 +5084,25 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G10">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.2254320318923924</v>
+        <v>-0.1665388026682479</v>
       </c>
       <c r="J10">
-        <v>0.03750206210014283</v>
+        <v>0.1280616578297019</v>
       </c>
       <c r="K10">
-        <v>-0.2757884146130811</v>
+        <v>-0.2014155913676093</v>
       </c>
       <c r="L10">
-        <v>0.05255329742499692</v>
+        <v>0.1607294756220496</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5122,25 +5122,25 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.1794340300657417</v>
+        <v>-0.1072157037809592</v>
       </c>
       <c r="J11">
-        <v>0.08321105252268295</v>
+        <v>0.3053256696332304</v>
       </c>
       <c r="K11">
-        <v>-0.2382169979796553</v>
+        <v>-0.1443212092158959</v>
       </c>
       <c r="L11">
-        <v>0.095728836361827</v>
+        <v>0.3173391327305688</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5160,25 +5160,25 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G12">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1869191683862415</v>
+        <v>0.2226979908645411</v>
       </c>
       <c r="J12">
-        <v>0.06934431565042681</v>
+        <v>0.03212529602718809</v>
       </c>
       <c r="K12">
-        <v>0.2610882725528407</v>
+        <v>0.3048932618757045</v>
       </c>
       <c r="L12">
-        <v>0.06704286140152567</v>
+        <v>0.03132317581227168</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -5201,22 +5201,22 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H13">
         <v>10</v>
       </c>
       <c r="I13">
-        <v>0.04969039949999533</v>
+        <v>0.05270462766947299</v>
       </c>
       <c r="J13">
-        <v>0.8509806870320558</v>
+        <v>0.8464505968765906</v>
       </c>
       <c r="K13">
-        <v>0.01262892050706804</v>
+        <v>0.0259499648053841</v>
       </c>
       <c r="L13">
-        <v>0.9723786419920799</v>
+        <v>0.9432726625041241</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -5239,22 +5239,22 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-0.149071198499986</v>
+        <v>-0.2635231383473649</v>
       </c>
       <c r="J14">
-        <v>0.5730251193553904</v>
+        <v>0.3329216080655659</v>
       </c>
       <c r="K14">
-        <v>-0.1894338076060206</v>
+        <v>-0.3503245248726853</v>
       </c>
       <c r="L14">
-        <v>0.6001664342511973</v>
+        <v>0.3209921486658833</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -5277,22 +5277,22 @@
         <v>10</v>
       </c>
       <c r="G15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-0.1256297269074015</v>
+        <v>-0.2398508059000617</v>
       </c>
       <c r="J15">
-        <v>0.6374017405958849</v>
+        <v>0.3819327979196356</v>
       </c>
       <c r="K15">
-        <v>-0.152008377581442</v>
+        <v>-0.3448837241706717</v>
       </c>
       <c r="L15">
-        <v>0.6750590889374006</v>
+        <v>0.3290799383310438</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -5315,22 +5315,22 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-0.298142396999972</v>
+        <v>-0.210818510677892</v>
       </c>
       <c r="J16">
-        <v>0.2596563563704499</v>
+        <v>0.4385780260809998</v>
       </c>
       <c r="K16">
-        <v>-0.3788676152120412</v>
+        <v>-0.259499648053841</v>
       </c>
       <c r="L16">
-        <v>0.2802942824523375</v>
+        <v>0.4690507582155354</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -5353,22 +5353,22 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17">
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-0.1987615979999813</v>
+        <v>-0.105409255338946</v>
       </c>
       <c r="J17">
-        <v>0.4523703606773608</v>
+        <v>0.6985353583033387</v>
       </c>
       <c r="K17">
-        <v>-0.3409808536908371</v>
+        <v>-0.1686747712349966</v>
       </c>
       <c r="L17">
-        <v>0.3349456951179903</v>
+        <v>0.6413437507268416</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -5391,22 +5391,22 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H18">
         <v>10</v>
       </c>
       <c r="I18">
-        <v>0.149071198499986</v>
+        <v>0.105409255338946</v>
       </c>
       <c r="J18">
-        <v>0.5730251193553904</v>
+        <v>0.6985353583033387</v>
       </c>
       <c r="K18">
-        <v>0.1641759665918845</v>
+        <v>0.1037998592215364</v>
       </c>
       <c r="L18">
-        <v>0.6503895621649565</v>
+        <v>0.7753684943458543</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -5429,22 +5429,22 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>0.07537783614444091</v>
+        <v>0.0266500895444513</v>
       </c>
       <c r="J19">
-        <v>0.7773295263554205</v>
+        <v>0.9226081041997291</v>
       </c>
       <c r="K19">
-        <v>0.1076726007868547</v>
+        <v>0.04555068055084343</v>
       </c>
       <c r="L19">
-        <v>0.7671778789420547</v>
+        <v>0.9005643729271482</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -5467,22 +5467,22 @@
         <v>10</v>
       </c>
       <c r="G20">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H20">
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-0.09938079899999065</v>
+        <v>-0.105409255338946</v>
       </c>
       <c r="J20">
-        <v>0.7071142312899612</v>
+        <v>0.6985353583033387</v>
       </c>
       <c r="K20">
-        <v>-0.1262892050706804</v>
+        <v>-0.07784989441615228</v>
       </c>
       <c r="L20">
-        <v>0.7281063840216824</v>
+        <v>0.8307317091592451</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5505,22 +5505,22 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-0.149071198499986</v>
+        <v>-0.05270462766947299</v>
       </c>
       <c r="J21">
-        <v>0.5730251193553904</v>
+        <v>0.8464505968765906</v>
       </c>
       <c r="K21">
-        <v>-0.2399494896342928</v>
+        <v>-0.1037998592215364</v>
       </c>
       <c r="L21">
-        <v>0.5043017190353258</v>
+        <v>0.7753684943458543</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -5543,22 +5543,22 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H22">
         <v>10</v>
       </c>
       <c r="I22">
-        <v>0.3975231959999626</v>
+        <v>0.3162277660168379</v>
       </c>
       <c r="J22">
-        <v>0.1328549557310538</v>
+        <v>0.2452781168067728</v>
       </c>
       <c r="K22">
-        <v>0.5304146612968577</v>
+        <v>0.3892494720807614</v>
       </c>
       <c r="L22">
-        <v>0.1147392659290222</v>
+        <v>0.2662240730692272</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -5581,22 +5581,22 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H23">
         <v>10</v>
       </c>
       <c r="I23">
-        <v>0.298142396999972</v>
+        <v>0.210818510677892</v>
       </c>
       <c r="J23">
-        <v>0.2596563563704499</v>
+        <v>0.4385780260809998</v>
       </c>
       <c r="K23">
-        <v>0.4041254562261773</v>
+        <v>0.2465246656511489</v>
       </c>
       <c r="L23">
-        <v>0.2467547295422347</v>
+        <v>0.492323476312569</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -5619,22 +5619,22 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H24">
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-0.2484519974999766</v>
+        <v>-0.1581138830084189</v>
       </c>
       <c r="J24">
-        <v>0.347558036741169</v>
+        <v>0.5612758361345778</v>
       </c>
       <c r="K24">
-        <v>-0.4293832972403134</v>
+        <v>-0.259499648053841</v>
       </c>
       <c r="L24">
-        <v>0.2155824117700313</v>
+        <v>0.4690507582155354</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -5654,25 +5654,13 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>16</v>
-      </c>
-      <c r="I25">
-        <v>-0.31352722326441</v>
-      </c>
-      <c r="J25">
-        <v>0.1131685336545776</v>
-      </c>
-      <c r="K25">
-        <v>-0.4479914656638877</v>
-      </c>
-      <c r="L25">
-        <v>0.08182143505121871</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5692,25 +5680,13 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>16</v>
-      </c>
-      <c r="I26">
-        <v>-0.3872983346207417</v>
-      </c>
-      <c r="J26">
-        <v>0.05036597579032801</v>
-      </c>
-      <c r="K26">
-        <v>-0.5070173682344674</v>
-      </c>
-      <c r="L26">
-        <v>0.04501930875693567</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -5730,25 +5706,13 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>16</v>
-      </c>
-      <c r="I27">
-        <v>0.08334047874242113</v>
-      </c>
-      <c r="J27">
-        <v>0.6747078413451294</v>
-      </c>
-      <c r="K27">
-        <v>0.08027373462987823</v>
-      </c>
-      <c r="L27">
-        <v>0.7675926515511813</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -5768,25 +5732,13 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>16</v>
-      </c>
-      <c r="I28">
-        <v>0.09338863578008762</v>
-      </c>
-      <c r="J28">
-        <v>0.6401498414586226</v>
-      </c>
-      <c r="K28">
-        <v>0.1305442024324843</v>
-      </c>
-      <c r="L28">
-        <v>0.6298840619248964</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -5806,25 +5758,13 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>16</v>
-      </c>
-      <c r="I29">
-        <v>0.1290994448735805</v>
-      </c>
-      <c r="J29">
-        <v>0.5142199988155506</v>
-      </c>
-      <c r="K29">
-        <v>0.1619428608987702</v>
-      </c>
-      <c r="L29">
-        <v>0.5490376092324329</v>
       </c>
     </row>
   </sheetData>

--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -504,9 +504,9 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -830,25 +830,25 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G9">
-        <v>483</v>
+        <v>983</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>-0.2266499931585039</v>
+        <v>-0.1862608333535023</v>
       </c>
       <c r="J9">
-        <v>0.001388944087542739</v>
+        <v>0.007684761637578328</v>
       </c>
       <c r="K9">
-        <v>-0.3292121926341289</v>
+        <v>-0.2793150240750672</v>
       </c>
       <c r="L9">
-        <v>0.0008243882531155807</v>
+        <v>0.004888736101567308</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -868,25 +868,25 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10">
-        <v>768</v>
+        <v>833</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>0.01866777293784236</v>
+        <v>0.1054257592623727</v>
       </c>
       <c r="J10">
-        <v>0.8583574614657677</v>
+        <v>0.3121424441080656</v>
       </c>
       <c r="K10">
-        <v>0.02926774595311432</v>
+        <v>0.1516674626809092</v>
       </c>
       <c r="L10">
-        <v>0.8401020874019567</v>
+        <v>0.2930643500882431</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -906,25 +906,25 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11">
-        <v>768</v>
+        <v>833</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>0.03525306566614442</v>
+        <v>0.1154391836616713</v>
       </c>
       <c r="J11">
-        <v>0.7244530391680126</v>
+        <v>0.2470336165569458</v>
       </c>
       <c r="K11">
-        <v>0.03962642574794883</v>
+        <v>0.1618182599138137</v>
       </c>
       <c r="L11">
-        <v>0.7846830695577185</v>
+        <v>0.2615624896516894</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -944,25 +944,25 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12">
-        <v>768</v>
+        <v>833</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1975428742000058</v>
+        <v>0.1387254219616285</v>
       </c>
       <c r="J12">
-        <v>0.04682237144660668</v>
+        <v>0.1615317577150278</v>
       </c>
       <c r="K12">
-        <v>0.2832674538277786</v>
+        <v>0.1997164940650696</v>
       </c>
       <c r="L12">
-        <v>0.04622012001137949</v>
+        <v>0.1643635862293704</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -4719,8 +4719,8 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
@@ -5046,25 +5046,25 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="G9">
-        <v>105</v>
+        <v>605</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>-0.1869261787362204</v>
+        <v>-0.1183225614658439</v>
       </c>
       <c r="J9">
-        <v>0.01502626043323942</v>
+        <v>0.120695698271125</v>
       </c>
       <c r="K9">
-        <v>-0.2423346744391451</v>
+        <v>-0.1603629383925238</v>
       </c>
       <c r="L9">
-        <v>0.01513196719297787</v>
+        <v>0.1109806238570996</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -5084,25 +5084,25 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="H10">
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.1665388026682479</v>
+        <v>-0.07902849116038421</v>
       </c>
       <c r="J10">
-        <v>0.1280616578297019</v>
+        <v>0.4685639401362257</v>
       </c>
       <c r="K10">
-        <v>-0.2014155913676093</v>
+        <v>-0.08451186021773145</v>
       </c>
       <c r="L10">
-        <v>0.1607294756220496</v>
+        <v>0.5595433967220398</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5122,25 +5122,25 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="H11">
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.1072157037809592</v>
+        <v>-0.03020353015662129</v>
       </c>
       <c r="J11">
-        <v>0.3053256696332304</v>
+        <v>0.771942188366149</v>
       </c>
       <c r="K11">
-        <v>-0.1443212092158959</v>
+        <v>-0.03236314557204496</v>
       </c>
       <c r="L11">
-        <v>0.3173391327305688</v>
+        <v>0.8234481009740228</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5160,25 +5160,25 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="H12">
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.2226979908645411</v>
+        <v>0.1508482658673557</v>
       </c>
       <c r="J12">
-        <v>0.03212529602718809</v>
+        <v>0.145163870500308</v>
       </c>
       <c r="K12">
-        <v>0.3048932618757045</v>
+        <v>0.2079035266272217</v>
       </c>
       <c r="L12">
-        <v>0.03132317581227168</v>
+        <v>0.1473930546093456</v>
       </c>
     </row>
     <row r="13" spans="1:12">

--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -1438,25 +1438,25 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H25">
         <v>16</v>
       </c>
       <c r="I25">
-        <v>-0.3208833147655317</v>
+        <v>-0.2089183206099184</v>
       </c>
       <c r="J25">
-        <v>0.1310095881916458</v>
+        <v>0.2858071051160878</v>
       </c>
       <c r="K25">
-        <v>-0.3615507630310936</v>
+        <v>-0.2761088800464458</v>
       </c>
       <c r="L25">
-        <v>0.1688293942897778</v>
+        <v>0.3006008438154604</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1476,25 +1476,25 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H26">
         <v>16</v>
       </c>
       <c r="I26">
-        <v>-0.1544993737759967</v>
+        <v>-0.1907515101220994</v>
       </c>
       <c r="J26">
-        <v>0.4671641537476017</v>
+        <v>0.3297832606788835</v>
       </c>
       <c r="K26">
-        <v>-0.1717366124397695</v>
+        <v>-0.2791264634349316</v>
       </c>
       <c r="L26">
-        <v>0.5247923002825454</v>
+        <v>0.2951316609645892</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1514,25 +1514,25 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H27">
         <v>16</v>
       </c>
       <c r="I27">
-        <v>0.3341631412724104</v>
+        <v>0.3648596387010686</v>
       </c>
       <c r="J27">
-        <v>0.1170517823729769</v>
+        <v>0.06317307481323101</v>
       </c>
       <c r="K27">
-        <v>0.3934758817437114</v>
+        <v>0.4446662347157511</v>
       </c>
       <c r="L27">
-        <v>0.1315976135653158</v>
+        <v>0.08439298705280707</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1552,25 +1552,25 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H28">
         <v>16</v>
       </c>
       <c r="I28">
-        <v>-0.4694027940381773</v>
+        <v>-0.1563850753205831</v>
       </c>
       <c r="J28">
-        <v>0.0286729854548637</v>
+        <v>0.4285752941987943</v>
       </c>
       <c r="K28">
-        <v>-0.5439282932204211</v>
+        <v>-0.2133681077431026</v>
       </c>
       <c r="L28">
-        <v>0.0294039628831014</v>
+        <v>0.4275202599269713</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1590,25 +1590,25 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H29">
         <v>16</v>
       </c>
       <c r="I29">
-        <v>0.05942283606769105</v>
+        <v>-0.1725846996342804</v>
       </c>
       <c r="J29">
-        <v>0.77974282876954</v>
+        <v>0.377919481405675</v>
       </c>
       <c r="K29">
-        <v>0.05423261445466403</v>
+        <v>-0.1931253368630878</v>
       </c>
       <c r="L29">
-        <v>0.841887936826351</v>
+        <v>0.4736035833560223</v>
       </c>
     </row>
   </sheetData>
@@ -4720,7 +4720,7 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
@@ -5654,13 +5654,25 @@
         <v>16</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H25">
         <v>16</v>
+      </c>
+      <c r="I25">
+        <v>-0.3244079990200284</v>
+      </c>
+      <c r="J25">
+        <v>0.1020809611324846</v>
+      </c>
+      <c r="K25">
+        <v>-0.4824165900576836</v>
+      </c>
+      <c r="L25">
+        <v>0.05842088299110668</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -5680,13 +5692,25 @@
         <v>16</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H26">
         <v>16</v>
+      </c>
+      <c r="I26">
+        <v>-0.4170959987400364</v>
+      </c>
+      <c r="J26">
+        <v>0.03555790569992093</v>
+      </c>
+      <c r="K26">
+        <v>-0.5355127556300702</v>
+      </c>
+      <c r="L26">
+        <v>0.03253137976639191</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -5706,13 +5730,25 @@
         <v>16</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H27">
         <v>16</v>
+      </c>
+      <c r="I27">
+        <v>0.2047685867790963</v>
+      </c>
+      <c r="J27">
+        <v>0.3037024766857317</v>
+      </c>
+      <c r="K27">
+        <v>0.2170954499333818</v>
+      </c>
+      <c r="L27">
+        <v>0.4192967698838219</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -5732,13 +5768,25 @@
         <v>16</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H28">
         <v>16</v>
+      </c>
+      <c r="I28">
+        <v>0.08448190755542286</v>
+      </c>
+      <c r="J28">
+        <v>0.6731676659685988</v>
+      </c>
+      <c r="K28">
+        <v>0.1201996807657877</v>
+      </c>
+      <c r="L28">
+        <v>0.6574684200274921</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -5758,13 +5806,25 @@
         <v>16</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H29">
         <v>16</v>
+      </c>
+      <c r="I29">
+        <v>0.009268799972000809</v>
+      </c>
+      <c r="J29">
+        <v>0.9627444106905073</v>
+      </c>
+      <c r="K29">
+        <v>0.01365329971861369</v>
+      </c>
+      <c r="L29">
+        <v>0.9599750222894384</v>
       </c>
     </row>
   </sheetData>

--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -503,7 +503,7 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>-0.3178304128441319</v>
       </c>
       <c r="L5">
-        <v>0.3140610795011266</v>
+        <v>0.3140610795011265</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -848,7 +848,7 @@
         <v>-0.2793150240750672</v>
       </c>
       <c r="L9">
-        <v>0.004888736101567308</v>
+        <v>0.004888736101567307</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -877,16 +877,16 @@
         <v>50</v>
       </c>
       <c r="I10">
-        <v>0.1054257592623727</v>
+        <v>-0.01788960397609135</v>
       </c>
       <c r="J10">
-        <v>0.3121424441080656</v>
+        <v>0.8831700141519032</v>
       </c>
       <c r="K10">
-        <v>0.1516674626809092</v>
+        <v>-0.01605248793883186</v>
       </c>
       <c r="L10">
-        <v>0.2930643500882431</v>
+        <v>0.9118983828429555</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -915,16 +915,16 @@
         <v>50</v>
       </c>
       <c r="I11">
-        <v>0.1154391836616713</v>
+        <v>-0.0319066731228802</v>
       </c>
       <c r="J11">
-        <v>0.2470336165569458</v>
+        <v>0.7837672300250216</v>
       </c>
       <c r="K11">
-        <v>0.1618182599138137</v>
+        <v>-0.03045075791865187</v>
       </c>
       <c r="L11">
-        <v>0.2615624896516894</v>
+        <v>0.8337285990222609</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -953,16 +953,16 @@
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1387254219616285</v>
+        <v>-0.2441570787714312</v>
       </c>
       <c r="J12">
-        <v>0.1615317577150278</v>
+        <v>0.03455416553919029</v>
       </c>
       <c r="K12">
-        <v>0.1997164940650696</v>
+        <v>-0.3094340106343606</v>
       </c>
       <c r="L12">
-        <v>0.1643635862293704</v>
+        <v>0.02876701130235892</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1266,7 +1266,7 @@
         <v>-0.4494665749754947</v>
       </c>
       <c r="L20">
-        <v>0.1925017251163437</v>
+        <v>0.1925017251163438</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1494,7 +1494,7 @@
         <v>-0.2791264634349316</v>
       </c>
       <c r="L26">
-        <v>0.2951316609645892</v>
+        <v>0.2951316609645891</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1631,7 +1631,7 @@
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1955,16 +1955,16 @@
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.1513701890060563</v>
+        <v>-0.01391413642584883</v>
       </c>
       <c r="J10">
-        <v>0.1849849928400071</v>
+        <v>0.9090032366864784</v>
       </c>
       <c r="K10">
-        <v>-0.1909099024833014</v>
+        <v>-0.02099889410603005</v>
       </c>
       <c r="L10">
-        <v>0.1841630933746127</v>
+        <v>0.8849122996084955</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1993,16 +1993,16 @@
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.1912266713473635</v>
+        <v>-0.02064549437362836</v>
       </c>
       <c r="J11">
-        <v>0.07966527054092901</v>
+        <v>0.8590674623402641</v>
       </c>
       <c r="K11">
-        <v>-0.2629384536176831</v>
+        <v>-0.02666748193481936</v>
       </c>
       <c r="L11">
-        <v>0.06506084897945322</v>
+        <v>0.854146214500382</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2031,16 +2031,16 @@
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.2310064793132821</v>
+        <v>-0.2553398457380617</v>
       </c>
       <c r="J12">
-        <v>0.03309841101323721</v>
+        <v>0.02708099412121601</v>
       </c>
       <c r="K12">
-        <v>0.2844439628835274</v>
+        <v>-0.312938777371799</v>
       </c>
       <c r="L12">
-        <v>0.04528302631069108</v>
+        <v>0.02691509407933328</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3081,16 +3081,16 @@
         <v>50</v>
       </c>
       <c r="I10">
-        <v>0.08712167584961492</v>
+        <v>-0.01391413642584883</v>
       </c>
       <c r="J10">
-        <v>0.4083766752312095</v>
+        <v>0.9090032366864784</v>
       </c>
       <c r="K10">
-        <v>0.1227687641955272</v>
+        <v>-0.01026612600739247</v>
       </c>
       <c r="L10">
-        <v>0.3956759834281137</v>
+        <v>0.9435901857829745</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3119,16 +3119,16 @@
         <v>50</v>
       </c>
       <c r="I11">
-        <v>0.07462967377124524</v>
+        <v>-0.02815294687312959</v>
       </c>
       <c r="J11">
-        <v>0.4588124610579571</v>
+        <v>0.8086800956106934</v>
       </c>
       <c r="K11">
-        <v>0.09255821810809323</v>
+        <v>-0.0299893827986723</v>
       </c>
       <c r="L11">
-        <v>0.5226237277667096</v>
+        <v>0.8362130272367809</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3157,16 +3157,16 @@
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.0648462728029752</v>
+        <v>-0.247884667760308</v>
       </c>
       <c r="J12">
-        <v>0.5171200381290717</v>
+        <v>0.03188792894690582</v>
       </c>
       <c r="K12">
-        <v>0.08638478532010939</v>
+        <v>-0.3096184720415943</v>
       </c>
       <c r="L12">
-        <v>0.5508414269428876</v>
+        <v>0.02866696147428331</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3833,8 +3833,8 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
   </cols>
@@ -4111,16 +4111,16 @@
         <v>50</v>
       </c>
       <c r="I10">
-        <v>0.01421997815784012</v>
+        <v>0.0764443486090874</v>
       </c>
       <c r="J10">
-        <v>0.9088173646349219</v>
+        <v>0.5354361824937546</v>
       </c>
       <c r="K10">
-        <v>0.01636148293791983</v>
+        <v>0.08747819195849275</v>
       </c>
       <c r="L10">
-        <v>0.9102093962355748</v>
+        <v>0.5457912421920483</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -4149,16 +4149,16 @@
         <v>50</v>
       </c>
       <c r="I11">
-        <v>0.001918117792161453</v>
+        <v>0.03127820821997541</v>
       </c>
       <c r="J11">
-        <v>0.9870933347767511</v>
+        <v>0.790617574368795</v>
       </c>
       <c r="K11">
-        <v>0.002310973073108823</v>
+        <v>0.03921851354723432</v>
       </c>
       <c r="L11">
-        <v>0.9872920353883015</v>
+        <v>0.7868474296660681</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -4187,16 +4187,16 @@
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.2419047619047619</v>
+        <v>-0.1983088195159672</v>
       </c>
       <c r="J12">
-        <v>0.04002718189621234</v>
+        <v>0.0901991606949034</v>
       </c>
       <c r="K12">
-        <v>0.2933526131391836</v>
+        <v>-0.2421980018747268</v>
       </c>
       <c r="L12">
-        <v>0.03867934687031339</v>
+        <v>0.09014837129941855</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -4721,7 +4721,7 @@
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4988,7 +4988,7 @@
         <v>-0.5561107852980067</v>
       </c>
       <c r="L7">
-        <v>0.06043495620092659</v>
+        <v>0.0604349562009266</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -5093,16 +5093,16 @@
         <v>50</v>
       </c>
       <c r="I10">
-        <v>-0.07902849116038421</v>
+        <v>-0.02584053907657639</v>
       </c>
       <c r="J10">
-        <v>0.4685639401362257</v>
+        <v>0.8319012317886401</v>
       </c>
       <c r="K10">
-        <v>-0.08451186021773145</v>
+        <v>-0.02491868767248899</v>
       </c>
       <c r="L10">
-        <v>0.5595433967220398</v>
+        <v>0.8636170341288709</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5131,16 +5131,16 @@
         <v>50</v>
       </c>
       <c r="I11">
-        <v>-0.03020353015662129</v>
+        <v>-0.02439922062337898</v>
       </c>
       <c r="J11">
-        <v>0.771942188366149</v>
+        <v>0.8337884478927275</v>
       </c>
       <c r="K11">
-        <v>-0.03236314557204496</v>
+        <v>-0.02888208251072132</v>
       </c>
       <c r="L11">
-        <v>0.8234481009740228</v>
+        <v>0.8421820698041393</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5169,16 +5169,16 @@
         <v>50</v>
       </c>
       <c r="I12">
-        <v>0.1508482658673557</v>
+        <v>-0.2516122567491849</v>
       </c>
       <c r="J12">
-        <v>0.145163870500308</v>
+        <v>0.02940004335865699</v>
       </c>
       <c r="K12">
-        <v>0.2079035266272217</v>
+        <v>-0.311094163299463</v>
       </c>
       <c r="L12">
-        <v>0.1473930546093456</v>
+        <v>0.02787696039183272</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -5710,7 +5710,7 @@
         <v>-0.5355127556300702</v>
       </c>
       <c r="L26">
-        <v>0.03253137976639191</v>
+        <v>0.03253137976639189</v>
       </c>
     </row>
     <row r="27" spans="1:12">

--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="51">
   <si>
     <t>metric</t>
   </si>
@@ -107,6 +107,45 @@
     <t>perc_correct_output</t>
   </si>
   <si>
+    <t>adjusted_gaze_sig</t>
+  </si>
+  <si>
+    <t>adjusted_gaze_non_sig</t>
+  </si>
+  <si>
+    <t>adjusted_fix_sig</t>
+  </si>
+  <si>
+    <t>adjusted_fix_non_sig</t>
+  </si>
+  <si>
+    <t>adjusted_gaze_flow</t>
+  </si>
+  <si>
+    <t>adjusted_gaze_non_flow</t>
+  </si>
+  <si>
+    <t>adjusted_fix_flow</t>
+  </si>
+  <si>
+    <t>adjusted_fix_non_flow</t>
+  </si>
+  <si>
+    <t>adjusted_gaze_call</t>
+  </si>
+  <si>
+    <t>adjusted_gaze_non_call</t>
+  </si>
+  <si>
+    <t>adjusted_fix_call</t>
+  </si>
+  <si>
+    <t>adjusted_fix_non_call</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
     <t>9_gc</t>
   </si>
   <si>
@@ -123,9 +162,6 @@
   </si>
   <si>
     <t>rating</t>
-  </si>
-  <si>
-    <t>time</t>
   </si>
   <si>
     <t>physiological</t>
@@ -492,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -504,9 +540,9 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -555,10 +591,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -593,10 +629,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>23</v>
@@ -631,10 +667,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -669,10 +705,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -696,7 +732,7 @@
         <v>-0.3178304128441319</v>
       </c>
       <c r="L5">
-        <v>0.3140610795011265</v>
+        <v>0.3140610795011266</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -707,10 +743,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -745,10 +781,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -783,10 +819,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -821,10 +857,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -848,7 +884,7 @@
         <v>-0.2793150240750672</v>
       </c>
       <c r="L9">
-        <v>0.004888736101567307</v>
+        <v>0.004888736101567308</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -859,10 +895,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -897,10 +933,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -935,10 +971,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -962,7 +998,7 @@
         <v>-0.3094340106343606</v>
       </c>
       <c r="L12">
-        <v>0.02876701130235892</v>
+        <v>0.02876701130235894</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -970,13 +1006,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1008,13 +1044,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -1046,13 +1082,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1084,13 +1120,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -1122,13 +1158,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1160,13 +1196,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -1198,13 +1234,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -1236,13 +1272,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -1266,7 +1302,7 @@
         <v>-0.4494665749754947</v>
       </c>
       <c r="L20">
-        <v>0.1925017251163438</v>
+        <v>0.1925017251163437</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1274,13 +1310,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -1312,13 +1348,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -1350,13 +1386,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -1388,13 +1424,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -1426,13 +1462,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -1464,13 +1500,13 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>16</v>
@@ -1494,7 +1530,7 @@
         <v>-0.2791264634349316</v>
       </c>
       <c r="L26">
-        <v>0.2951316609645891</v>
+        <v>0.2951316609645892</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1502,13 +1538,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>16</v>
@@ -1540,13 +1576,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28">
         <v>16</v>
@@ -1578,13 +1614,13 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>16</v>
@@ -1609,6 +1645,449 @@
       </c>
       <c r="L29">
         <v>0.4736035833560223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>64</v>
+      </c>
+      <c r="F30">
+        <v>62</v>
+      </c>
+      <c r="G30">
+        <v>963</v>
+      </c>
+      <c r="H30">
+        <v>64</v>
+      </c>
+      <c r="I30">
+        <v>0.3418050362170402</v>
+      </c>
+      <c r="J30">
+        <v>0.001004349555378589</v>
+      </c>
+      <c r="K30">
+        <v>0.4056114839282338</v>
+      </c>
+      <c r="L30">
+        <v>0.0008838558860104442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>62</v>
+      </c>
+      <c r="G31">
+        <v>963</v>
+      </c>
+      <c r="H31">
+        <v>64</v>
+      </c>
+      <c r="I31">
+        <v>0.279314216373952</v>
+      </c>
+      <c r="J31">
+        <v>0.006440592968704181</v>
+      </c>
+      <c r="K31">
+        <v>0.3562627675046445</v>
+      </c>
+      <c r="L31">
+        <v>0.003859966882439438</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>64</v>
+      </c>
+      <c r="F32">
+        <v>62</v>
+      </c>
+      <c r="G32">
+        <v>963</v>
+      </c>
+      <c r="H32">
+        <v>64</v>
+      </c>
+      <c r="I32">
+        <v>0.3152570722390177</v>
+      </c>
+      <c r="J32">
+        <v>0.002414741112708488</v>
+      </c>
+      <c r="K32">
+        <v>0.3790655710532781</v>
+      </c>
+      <c r="L32">
+        <v>0.002008860935731097</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>62</v>
+      </c>
+      <c r="G33">
+        <v>963</v>
+      </c>
+      <c r="H33">
+        <v>64</v>
+      </c>
+      <c r="I33">
+        <v>0.3034624195186741</v>
+      </c>
+      <c r="J33">
+        <v>0.003076304955910668</v>
+      </c>
+      <c r="K33">
+        <v>0.3774523130235019</v>
+      </c>
+      <c r="L33">
+        <v>0.002107109964675385</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34">
+        <v>64</v>
+      </c>
+      <c r="F34">
+        <v>62</v>
+      </c>
+      <c r="G34">
+        <v>963</v>
+      </c>
+      <c r="H34">
+        <v>64</v>
+      </c>
+      <c r="I34">
+        <v>0.3645312773432739</v>
+      </c>
+      <c r="J34">
+        <v>0.0004312956077763248</v>
+      </c>
+      <c r="K34">
+        <v>0.4372373621113425</v>
+      </c>
+      <c r="L34">
+        <v>0.0003031157737914172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>64</v>
+      </c>
+      <c r="F35">
+        <v>62</v>
+      </c>
+      <c r="G35">
+        <v>963</v>
+      </c>
+      <c r="H35">
+        <v>64</v>
+      </c>
+      <c r="I35">
+        <v>0.3176259577539492</v>
+      </c>
+      <c r="J35">
+        <v>0.002086286721444307</v>
+      </c>
+      <c r="K35">
+        <v>0.3904345772342148</v>
+      </c>
+      <c r="L35">
+        <v>0.001425026545059507</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36">
+        <v>64</v>
+      </c>
+      <c r="F36">
+        <v>62</v>
+      </c>
+      <c r="G36">
+        <v>963</v>
+      </c>
+      <c r="H36">
+        <v>64</v>
+      </c>
+      <c r="I36">
+        <v>0.3612397985410773</v>
+      </c>
+      <c r="J36">
+        <v>0.0004859755544250555</v>
+      </c>
+      <c r="K36">
+        <v>0.4397104595271652</v>
+      </c>
+      <c r="L36">
+        <v>0.0002775364452370338</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37">
+        <v>64</v>
+      </c>
+      <c r="F37">
+        <v>62</v>
+      </c>
+      <c r="G37">
+        <v>963</v>
+      </c>
+      <c r="H37">
+        <v>64</v>
+      </c>
+      <c r="I37">
+        <v>0.3274241878131969</v>
+      </c>
+      <c r="J37">
+        <v>0.001510770054291855</v>
+      </c>
+      <c r="K37">
+        <v>0.3996920472516634</v>
+      </c>
+      <c r="L37">
+        <v>0.001067701210651935</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>63</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>64</v>
+      </c>
+      <c r="F38">
+        <v>62</v>
+      </c>
+      <c r="G38">
+        <v>963</v>
+      </c>
+      <c r="H38">
+        <v>64</v>
+      </c>
+      <c r="I38">
+        <v>0.1907708048433044</v>
+      </c>
+      <c r="J38">
+        <v>0.06277226494783034</v>
+      </c>
+      <c r="K38">
+        <v>0.2221963583386178</v>
+      </c>
+      <c r="L38">
+        <v>0.07761946126493192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>64</v>
+      </c>
+      <c r="F39">
+        <v>62</v>
+      </c>
+      <c r="G39">
+        <v>963</v>
+      </c>
+      <c r="H39">
+        <v>64</v>
+      </c>
+      <c r="I39">
+        <v>0.4177639144036919</v>
+      </c>
+      <c r="J39">
+        <v>4.603037684741663E-05</v>
+      </c>
+      <c r="K39">
+        <v>0.5197470712523259</v>
+      </c>
+      <c r="L39">
+        <v>1.076278914057353E-05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>64</v>
+      </c>
+      <c r="F40">
+        <v>62</v>
+      </c>
+      <c r="G40">
+        <v>963</v>
+      </c>
+      <c r="H40">
+        <v>64</v>
+      </c>
+      <c r="I40">
+        <v>0.1988202058915451</v>
+      </c>
+      <c r="J40">
+        <v>0.05246287758794487</v>
+      </c>
+      <c r="K40">
+        <v>0.2425816291370515</v>
+      </c>
+      <c r="L40">
+        <v>0.05343862528962646</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <v>64</v>
+      </c>
+      <c r="F41">
+        <v>62</v>
+      </c>
+      <c r="G41">
+        <v>963</v>
+      </c>
+      <c r="H41">
+        <v>64</v>
+      </c>
+      <c r="I41">
+        <v>0.4161540341940438</v>
+      </c>
+      <c r="J41">
+        <v>4.923775603069727E-05</v>
+      </c>
+      <c r="K41">
+        <v>0.5133438071320287</v>
+      </c>
+      <c r="L41">
+        <v>1.439640264622759E-05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42">
+        <v>20</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +2097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -1630,9 +2109,9 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1681,10 +2160,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -1719,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>23</v>
@@ -1757,10 +2236,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -1795,10 +2274,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -1821,10 +2300,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -1847,10 +2326,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -1873,10 +2352,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1899,10 +2378,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1937,10 +2416,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -1975,10 +2454,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -2013,10 +2492,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -2040,7 +2519,7 @@
         <v>-0.312938777371799</v>
       </c>
       <c r="L12">
-        <v>0.02691509407933328</v>
+        <v>0.02691509407933329</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2048,13 +2527,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -2086,13 +2565,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -2124,13 +2603,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -2162,13 +2641,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -2200,13 +2679,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -2238,13 +2717,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -2276,13 +2755,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -2314,13 +2793,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2352,13 +2831,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -2390,13 +2869,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -2428,13 +2907,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -2466,13 +2945,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -2504,13 +2983,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -2542,13 +3021,13 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>16</v>
@@ -2580,13 +3059,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>16</v>
@@ -2618,13 +3097,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28">
         <v>16</v>
@@ -2656,13 +3135,13 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>16</v>
@@ -2687,6 +3166,449 @@
       </c>
       <c r="L29">
         <v>0.2669012522950682</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>64</v>
+      </c>
+      <c r="F30">
+        <v>26</v>
+      </c>
+      <c r="G30">
+        <v>61</v>
+      </c>
+      <c r="H30">
+        <v>64</v>
+      </c>
+      <c r="I30">
+        <v>0.2719614374971822</v>
+      </c>
+      <c r="J30">
+        <v>0.01002854427435773</v>
+      </c>
+      <c r="K30">
+        <v>0.3133954770236209</v>
+      </c>
+      <c r="L30">
+        <v>0.01168143094910069</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>26</v>
+      </c>
+      <c r="G31">
+        <v>61</v>
+      </c>
+      <c r="H31">
+        <v>64</v>
+      </c>
+      <c r="I31">
+        <v>0.2736099381762394</v>
+      </c>
+      <c r="J31">
+        <v>0.008646828924648913</v>
+      </c>
+      <c r="K31">
+        <v>0.3503163560182605</v>
+      </c>
+      <c r="L31">
+        <v>0.004542269001287748</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>64</v>
+      </c>
+      <c r="F32">
+        <v>26</v>
+      </c>
+      <c r="G32">
+        <v>61</v>
+      </c>
+      <c r="H32">
+        <v>64</v>
+      </c>
+      <c r="I32">
+        <v>0.2153788565413926</v>
+      </c>
+      <c r="J32">
+        <v>0.04143627362695777</v>
+      </c>
+      <c r="K32">
+        <v>0.2572745950545759</v>
+      </c>
+      <c r="L32">
+        <v>0.04013875927915869</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>26</v>
+      </c>
+      <c r="G33">
+        <v>61</v>
+      </c>
+      <c r="H33">
+        <v>64</v>
+      </c>
+      <c r="I33">
+        <v>0.31434151473322</v>
+      </c>
+      <c r="J33">
+        <v>0.002556326771866221</v>
+      </c>
+      <c r="K33">
+        <v>0.3876039941421227</v>
+      </c>
+      <c r="L33">
+        <v>0.001553979051888317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34">
+        <v>64</v>
+      </c>
+      <c r="F34">
+        <v>26</v>
+      </c>
+      <c r="G34">
+        <v>61</v>
+      </c>
+      <c r="H34">
+        <v>64</v>
+      </c>
+      <c r="I34">
+        <v>0.3539302241613812</v>
+      </c>
+      <c r="J34">
+        <v>0.000772349952058487</v>
+      </c>
+      <c r="K34">
+        <v>0.424200451879057</v>
+      </c>
+      <c r="L34">
+        <v>0.000477197190019958</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>64</v>
+      </c>
+      <c r="F35">
+        <v>26</v>
+      </c>
+      <c r="G35">
+        <v>61</v>
+      </c>
+      <c r="H35">
+        <v>64</v>
+      </c>
+      <c r="I35">
+        <v>0.2811386444097411</v>
+      </c>
+      <c r="J35">
+        <v>0.007360365207894896</v>
+      </c>
+      <c r="K35">
+        <v>0.3230085112671829</v>
+      </c>
+      <c r="L35">
+        <v>0.009232404757910088</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36">
+        <v>64</v>
+      </c>
+      <c r="F36">
+        <v>26</v>
+      </c>
+      <c r="G36">
+        <v>61</v>
+      </c>
+      <c r="H36">
+        <v>64</v>
+      </c>
+      <c r="I36">
+        <v>0.3340159915998713</v>
+      </c>
+      <c r="J36">
+        <v>0.001507047945669149</v>
+      </c>
+      <c r="K36">
+        <v>0.4072974713242659</v>
+      </c>
+      <c r="L36">
+        <v>0.0008370102382895101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37">
+        <v>64</v>
+      </c>
+      <c r="F37">
+        <v>26</v>
+      </c>
+      <c r="G37">
+        <v>61</v>
+      </c>
+      <c r="H37">
+        <v>64</v>
+      </c>
+      <c r="I37">
+        <v>0.2955099489163094</v>
+      </c>
+      <c r="J37">
+        <v>0.004846165788434817</v>
+      </c>
+      <c r="K37">
+        <v>0.3392314510102669</v>
+      </c>
+      <c r="L37">
+        <v>0.006103124812987851</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>63</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>64</v>
+      </c>
+      <c r="F38">
+        <v>26</v>
+      </c>
+      <c r="G38">
+        <v>61</v>
+      </c>
+      <c r="H38">
+        <v>64</v>
+      </c>
+      <c r="I38">
+        <v>0.1726664658393744</v>
+      </c>
+      <c r="J38">
+        <v>0.09751909882925842</v>
+      </c>
+      <c r="K38">
+        <v>0.2181695020568528</v>
+      </c>
+      <c r="L38">
+        <v>0.08329383026399091</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>64</v>
+      </c>
+      <c r="F39">
+        <v>26</v>
+      </c>
+      <c r="G39">
+        <v>61</v>
+      </c>
+      <c r="H39">
+        <v>64</v>
+      </c>
+      <c r="I39">
+        <v>0.362156843734893</v>
+      </c>
+      <c r="J39">
+        <v>0.0005099871944660304</v>
+      </c>
+      <c r="K39">
+        <v>0.4336277844655613</v>
+      </c>
+      <c r="L39">
+        <v>0.0003443273285276675</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>64</v>
+      </c>
+      <c r="F40">
+        <v>26</v>
+      </c>
+      <c r="G40">
+        <v>61</v>
+      </c>
+      <c r="H40">
+        <v>64</v>
+      </c>
+      <c r="I40">
+        <v>0.1903758469511051</v>
+      </c>
+      <c r="J40">
+        <v>0.06770717172115204</v>
+      </c>
+      <c r="K40">
+        <v>0.2372484551363874</v>
+      </c>
+      <c r="L40">
+        <v>0.05907598619468462</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <v>64</v>
+      </c>
+      <c r="F41">
+        <v>26</v>
+      </c>
+      <c r="G41">
+        <v>61</v>
+      </c>
+      <c r="H41">
+        <v>64</v>
+      </c>
+      <c r="I41">
+        <v>0.3568440294013737</v>
+      </c>
+      <c r="J41">
+        <v>0.0006159986891418091</v>
+      </c>
+      <c r="K41">
+        <v>0.4270673023540021</v>
+      </c>
+      <c r="L41">
+        <v>0.0004325469834795152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +3618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -2708,9 +3630,9 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2759,10 +3681,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -2797,10 +3719,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>23</v>
@@ -2835,10 +3757,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -2873,10 +3795,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -2911,10 +3833,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -2949,10 +3871,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -2987,10 +3909,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -3025,10 +3947,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3063,10 +3985,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -3101,10 +4023,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -3139,10 +4061,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -3166,7 +4088,7 @@
         <v>-0.3096184720415943</v>
       </c>
       <c r="L12">
-        <v>0.02866696147428331</v>
+        <v>0.02866696147428332</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3174,13 +4096,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -3212,13 +4134,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -3250,13 +4172,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -3288,13 +4210,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -3326,13 +4248,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -3364,13 +4286,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -3402,13 +4324,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -3440,13 +4362,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -3478,13 +4400,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -3516,13 +4438,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -3554,13 +4476,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -3592,13 +4514,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -3630,13 +4552,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -3668,13 +4590,13 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>16</v>
@@ -3706,13 +4628,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>16</v>
@@ -3744,13 +4666,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28">
         <v>16</v>
@@ -3782,13 +4704,13 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>16</v>
@@ -3813,6 +4735,449 @@
       </c>
       <c r="L29">
         <v>0.8878693028318899</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>64</v>
+      </c>
+      <c r="F30">
+        <v>51</v>
+      </c>
+      <c r="G30">
+        <v>305</v>
+      </c>
+      <c r="H30">
+        <v>64</v>
+      </c>
+      <c r="I30">
+        <v>0.3312066789974757</v>
+      </c>
+      <c r="J30">
+        <v>0.001444545715640912</v>
+      </c>
+      <c r="K30">
+        <v>0.3951613500511048</v>
+      </c>
+      <c r="L30">
+        <v>0.001230998474304181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>51</v>
+      </c>
+      <c r="G31">
+        <v>305</v>
+      </c>
+      <c r="H31">
+        <v>64</v>
+      </c>
+      <c r="I31">
+        <v>0.2851095580779748</v>
+      </c>
+      <c r="J31">
+        <v>0.005444291726857445</v>
+      </c>
+      <c r="K31">
+        <v>0.3585898901910007</v>
+      </c>
+      <c r="L31">
+        <v>0.003618737360339382</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>64</v>
+      </c>
+      <c r="F32">
+        <v>51</v>
+      </c>
+      <c r="G32">
+        <v>305</v>
+      </c>
+      <c r="H32">
+        <v>64</v>
+      </c>
+      <c r="I32">
+        <v>0.298003001904997</v>
+      </c>
+      <c r="J32">
+        <v>0.004153780499267119</v>
+      </c>
+      <c r="K32">
+        <v>0.3693068803776852</v>
+      </c>
+      <c r="L32">
+        <v>0.002671858328610249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>51</v>
+      </c>
+      <c r="G33">
+        <v>305</v>
+      </c>
+      <c r="H33">
+        <v>64</v>
+      </c>
+      <c r="I33">
+        <v>0.3092713850337354</v>
+      </c>
+      <c r="J33">
+        <v>0.002569376231396744</v>
+      </c>
+      <c r="K33">
+        <v>0.3769339037247535</v>
+      </c>
+      <c r="L33">
+        <v>0.002139581888614954</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34">
+        <v>64</v>
+      </c>
+      <c r="F34">
+        <v>51</v>
+      </c>
+      <c r="G34">
+        <v>305</v>
+      </c>
+      <c r="H34">
+        <v>64</v>
+      </c>
+      <c r="I34">
+        <v>0.3606202670394066</v>
+      </c>
+      <c r="J34">
+        <v>0.0005004520767949459</v>
+      </c>
+      <c r="K34">
+        <v>0.4411592251170234</v>
+      </c>
+      <c r="L34">
+        <v>0.000263484125366215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>64</v>
+      </c>
+      <c r="F35">
+        <v>51</v>
+      </c>
+      <c r="G35">
+        <v>305</v>
+      </c>
+      <c r="H35">
+        <v>64</v>
+      </c>
+      <c r="I35">
+        <v>0.3022825375654209</v>
+      </c>
+      <c r="J35">
+        <v>0.003417872613560628</v>
+      </c>
+      <c r="K35">
+        <v>0.3773506763775762</v>
+      </c>
+      <c r="L35">
+        <v>0.002113441279970249</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36">
+        <v>64</v>
+      </c>
+      <c r="F36">
+        <v>51</v>
+      </c>
+      <c r="G36">
+        <v>305</v>
+      </c>
+      <c r="H36">
+        <v>64</v>
+      </c>
+      <c r="I36">
+        <v>0.363913602811456</v>
+      </c>
+      <c r="J36">
+        <v>0.0004442465007961315</v>
+      </c>
+      <c r="K36">
+        <v>0.4439454280006037</v>
+      </c>
+      <c r="L36">
+        <v>0.0002382722252024225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37">
+        <v>64</v>
+      </c>
+      <c r="F37">
+        <v>51</v>
+      </c>
+      <c r="G37">
+        <v>305</v>
+      </c>
+      <c r="H37">
+        <v>64</v>
+      </c>
+      <c r="I37">
+        <v>0.3088183762154841</v>
+      </c>
+      <c r="J37">
+        <v>0.002783248451265792</v>
+      </c>
+      <c r="K37">
+        <v>0.38679535297946</v>
+      </c>
+      <c r="L37">
+        <v>0.001592694770480384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>63</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>64</v>
+      </c>
+      <c r="F38">
+        <v>51</v>
+      </c>
+      <c r="G38">
+        <v>305</v>
+      </c>
+      <c r="H38">
+        <v>64</v>
+      </c>
+      <c r="I38">
+        <v>0.2029593464283888</v>
+      </c>
+      <c r="J38">
+        <v>0.0478581302625294</v>
+      </c>
+      <c r="K38">
+        <v>0.2294084390662924</v>
+      </c>
+      <c r="L38">
+        <v>0.0682278542017089</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>64</v>
+      </c>
+      <c r="F39">
+        <v>51</v>
+      </c>
+      <c r="G39">
+        <v>305</v>
+      </c>
+      <c r="H39">
+        <v>64</v>
+      </c>
+      <c r="I39">
+        <v>0.3962539620744734</v>
+      </c>
+      <c r="J39">
+        <v>0.000111988463487014</v>
+      </c>
+      <c r="K39">
+        <v>0.5058369465496242</v>
+      </c>
+      <c r="L39">
+        <v>2.00978250431268E-05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>64</v>
+      </c>
+      <c r="F40">
+        <v>51</v>
+      </c>
+      <c r="G40">
+        <v>305</v>
+      </c>
+      <c r="H40">
+        <v>64</v>
+      </c>
+      <c r="I40">
+        <v>0.2174564426018452</v>
+      </c>
+      <c r="J40">
+        <v>0.034009720061427</v>
+      </c>
+      <c r="K40">
+        <v>0.2521760511419114</v>
+      </c>
+      <c r="L40">
+        <v>0.04440330791153663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <v>64</v>
+      </c>
+      <c r="F41">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>305</v>
+      </c>
+      <c r="H41">
+        <v>64</v>
+      </c>
+      <c r="I41">
+        <v>0.3946431736107561</v>
+      </c>
+      <c r="J41">
+        <v>0.0001194128933263328</v>
+      </c>
+      <c r="K41">
+        <v>0.4992788843756686</v>
+      </c>
+      <c r="L41">
+        <v>2.67281327133127E-05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42">
+        <v>18</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3822,7 +5187,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -3833,8 +5198,8 @@
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
   </cols>
@@ -3885,10 +5250,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -3911,10 +5276,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>23</v>
@@ -3937,10 +5302,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -3963,10 +5328,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -3989,10 +5354,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -4015,10 +5380,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -4041,10 +5406,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -4067,10 +5432,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -4093,10 +5458,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -4131,10 +5496,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -4169,10 +5534,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -4204,13 +5569,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -4230,13 +5595,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -4256,13 +5621,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -4282,13 +5647,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -4308,13 +5673,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -4334,13 +5699,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -4360,13 +5725,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -4386,13 +5751,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -4412,13 +5777,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -4438,13 +5803,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -4464,13 +5829,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -4490,13 +5855,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -4516,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -4554,13 +5919,13 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>16</v>
@@ -4592,13 +5957,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>16</v>
@@ -4630,13 +5995,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28">
         <v>16</v>
@@ -4668,13 +6033,13 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>16</v>
@@ -4699,6 +6064,449 @@
       </c>
       <c r="L29">
         <v>0.2457251662216493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>64</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>64</v>
+      </c>
+      <c r="I30">
+        <v>0.154410245264114</v>
+      </c>
+      <c r="J30">
+        <v>0.1586215146140932</v>
+      </c>
+      <c r="K30">
+        <v>0.1784665331291909</v>
+      </c>
+      <c r="L30">
+        <v>0.1582597890195718</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>64</v>
+      </c>
+      <c r="I31">
+        <v>0.1110401554529692</v>
+      </c>
+      <c r="J31">
+        <v>0.3041329983824486</v>
+      </c>
+      <c r="K31">
+        <v>0.1292816191680598</v>
+      </c>
+      <c r="L31">
+        <v>0.3086070485873409</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>64</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>64</v>
+      </c>
+      <c r="I32">
+        <v>0.1108120583660112</v>
+      </c>
+      <c r="J32">
+        <v>0.3116894041491827</v>
+      </c>
+      <c r="K32">
+        <v>0.1290992813744641</v>
+      </c>
+      <c r="L32">
+        <v>0.3092956578811401</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>64</v>
+      </c>
+      <c r="I33">
+        <v>0.1286655769534405</v>
+      </c>
+      <c r="J33">
+        <v>0.2337621546656686</v>
+      </c>
+      <c r="K33">
+        <v>0.1495119768620184</v>
+      </c>
+      <c r="L33">
+        <v>0.2383331150178653</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34">
+        <v>64</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>64</v>
+      </c>
+      <c r="I34">
+        <v>0.01261261261261261</v>
+      </c>
+      <c r="J34">
+        <v>0.9080089441723674</v>
+      </c>
+      <c r="K34">
+        <v>0.01481872766605732</v>
+      </c>
+      <c r="L34">
+        <v>0.9074784715786415</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>64</v>
+      </c>
+      <c r="F35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>64</v>
+      </c>
+      <c r="I35">
+        <v>0.1555469803845435</v>
+      </c>
+      <c r="J35">
+        <v>0.1527384056084066</v>
+      </c>
+      <c r="K35">
+        <v>0.180357734309281</v>
+      </c>
+      <c r="L35">
+        <v>0.1538252679335352</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36">
+        <v>64</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>64</v>
+      </c>
+      <c r="I36">
+        <v>0.005405405405405405</v>
+      </c>
+      <c r="J36">
+        <v>0.9605036540075619</v>
+      </c>
+      <c r="K36">
+        <v>0.006629430797973012</v>
+      </c>
+      <c r="L36">
+        <v>0.9585360952984102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37">
+        <v>64</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <v>64</v>
+      </c>
+      <c r="I37">
+        <v>0.177001736299653</v>
+      </c>
+      <c r="J37">
+        <v>0.103703844554033</v>
+      </c>
+      <c r="K37">
+        <v>0.205596168604444</v>
+      </c>
+      <c r="L37">
+        <v>0.1031405086222128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>63</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>64</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+      <c r="H38">
+        <v>64</v>
+      </c>
+      <c r="I38">
+        <v>0.1639164199543831</v>
+      </c>
+      <c r="J38">
+        <v>0.1292795358522291</v>
+      </c>
+      <c r="K38">
+        <v>0.1882386615904536</v>
+      </c>
+      <c r="L38">
+        <v>0.1363344811523539</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>64</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <v>64</v>
+      </c>
+      <c r="I39">
+        <v>0.03701338515098974</v>
+      </c>
+      <c r="J39">
+        <v>0.7319468844486436</v>
+      </c>
+      <c r="K39">
+        <v>0.0452774672198123</v>
+      </c>
+      <c r="L39">
+        <v>0.7223926005875032</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>64</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>64</v>
+      </c>
+      <c r="I40">
+        <v>0.2238428530559856</v>
+      </c>
+      <c r="J40">
+        <v>0.03830904740105989</v>
+      </c>
+      <c r="K40">
+        <v>0.2612606193619808</v>
+      </c>
+      <c r="L40">
+        <v>0.03704586833254033</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <v>64</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>64</v>
+      </c>
+      <c r="I41">
+        <v>-0.001762542150047131</v>
+      </c>
+      <c r="J41">
+        <v>0.9869860580944546</v>
+      </c>
+      <c r="K41">
+        <v>0.000770680293103188</v>
+      </c>
+      <c r="L41">
+        <v>0.9951776750792758</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4708,7 +6516,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -4720,9 +6528,9 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -4771,10 +6579,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E2">
         <v>23</v>
@@ -4809,10 +6617,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>23</v>
@@ -4847,10 +6655,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>23</v>
@@ -4885,10 +6693,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -4923,10 +6731,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -4961,10 +6769,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -4988,7 +6796,7 @@
         <v>-0.5561107852980067</v>
       </c>
       <c r="L7">
-        <v>0.0604349562009266</v>
+        <v>0.06043495620092659</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -4999,10 +6807,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -5037,10 +6845,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -5075,10 +6883,10 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -5113,10 +6921,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -5151,10 +6959,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -5178,7 +6986,7 @@
         <v>-0.311094163299463</v>
       </c>
       <c r="L12">
-        <v>0.02787696039183272</v>
+        <v>0.02787696039183273</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -5186,13 +6994,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -5224,13 +7032,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -5262,13 +7070,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -5300,13 +7108,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>10</v>
@@ -5338,13 +7146,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -5376,13 +7184,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -5414,13 +7222,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -5452,13 +7260,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -5490,13 +7298,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -5528,13 +7336,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -5566,13 +7374,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -5604,13 +7412,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -5642,13 +7450,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>16</v>
@@ -5680,13 +7488,13 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26">
         <v>16</v>
@@ -5710,7 +7518,7 @@
         <v>-0.5355127556300702</v>
       </c>
       <c r="L26">
-        <v>0.03253137976639189</v>
+        <v>0.03253137976639191</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -5718,13 +7526,13 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E27">
         <v>16</v>
@@ -5756,13 +7564,13 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28">
         <v>16</v>
@@ -5794,13 +7602,13 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E29">
         <v>16</v>
@@ -5825,6 +7633,449 @@
       </c>
       <c r="L29">
         <v>0.9599750222894384</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30">
+        <v>64</v>
+      </c>
+      <c r="F30">
+        <v>49</v>
+      </c>
+      <c r="G30">
+        <v>593</v>
+      </c>
+      <c r="H30">
+        <v>64</v>
+      </c>
+      <c r="I30">
+        <v>0.3276113363986184</v>
+      </c>
+      <c r="J30">
+        <v>0.001655631257960234</v>
+      </c>
+      <c r="K30">
+        <v>0.3991009701707551</v>
+      </c>
+      <c r="L30">
+        <v>0.001087833473222033</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>49</v>
+      </c>
+      <c r="G31">
+        <v>593</v>
+      </c>
+      <c r="H31">
+        <v>64</v>
+      </c>
+      <c r="I31">
+        <v>0.3025354644790327</v>
+      </c>
+      <c r="J31">
+        <v>0.003233526189215585</v>
+      </c>
+      <c r="K31">
+        <v>0.3718518389264061</v>
+      </c>
+      <c r="L31">
+        <v>0.002482411365845201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>64</v>
+      </c>
+      <c r="F32">
+        <v>49</v>
+      </c>
+      <c r="G32">
+        <v>593</v>
+      </c>
+      <c r="H32">
+        <v>64</v>
+      </c>
+      <c r="I32">
+        <v>0.3093183176149393</v>
+      </c>
+      <c r="J32">
+        <v>0.0029754480217311</v>
+      </c>
+      <c r="K32">
+        <v>0.3779946688636478</v>
+      </c>
+      <c r="L32">
+        <v>0.002073610609920638</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>49</v>
+      </c>
+      <c r="G33">
+        <v>593</v>
+      </c>
+      <c r="H33">
+        <v>64</v>
+      </c>
+      <c r="I33">
+        <v>0.3235112566829123</v>
+      </c>
+      <c r="J33">
+        <v>0.001639540198139356</v>
+      </c>
+      <c r="K33">
+        <v>0.3928883822267352</v>
+      </c>
+      <c r="L33">
+        <v>0.001321114481430784</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>63</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34">
+        <v>64</v>
+      </c>
+      <c r="F34">
+        <v>49</v>
+      </c>
+      <c r="G34">
+        <v>593</v>
+      </c>
+      <c r="H34">
+        <v>64</v>
+      </c>
+      <c r="I34">
+        <v>0.3604076213996629</v>
+      </c>
+      <c r="J34">
+        <v>0.0005149830017394812</v>
+      </c>
+      <c r="K34">
+        <v>0.4338907809518547</v>
+      </c>
+      <c r="L34">
+        <v>0.0003411602703865751</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>63</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>64</v>
+      </c>
+      <c r="F35">
+        <v>49</v>
+      </c>
+      <c r="G35">
+        <v>593</v>
+      </c>
+      <c r="H35">
+        <v>64</v>
+      </c>
+      <c r="I35">
+        <v>0.318344569436641</v>
+      </c>
+      <c r="J35">
+        <v>0.002084025119649695</v>
+      </c>
+      <c r="K35">
+        <v>0.386943018934536</v>
+      </c>
+      <c r="L35">
+        <v>0.001585560908767367</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36">
+        <v>64</v>
+      </c>
+      <c r="F36">
+        <v>49</v>
+      </c>
+      <c r="G36">
+        <v>593</v>
+      </c>
+      <c r="H36">
+        <v>64</v>
+      </c>
+      <c r="I36">
+        <v>0.3604076213996629</v>
+      </c>
+      <c r="J36">
+        <v>0.0005149830017394812</v>
+      </c>
+      <c r="K36">
+        <v>0.438023372270539</v>
+      </c>
+      <c r="L36">
+        <v>0.0002947617347795054</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37">
+        <v>64</v>
+      </c>
+      <c r="F37">
+        <v>49</v>
+      </c>
+      <c r="G37">
+        <v>593</v>
+      </c>
+      <c r="H37">
+        <v>64</v>
+      </c>
+      <c r="I37">
+        <v>0.3281649674655348</v>
+      </c>
+      <c r="J37">
+        <v>0.001509037284530193</v>
+      </c>
+      <c r="K37">
+        <v>0.3974792906174389</v>
+      </c>
+      <c r="L37">
+        <v>0.001144838922675296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>63</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38">
+        <v>64</v>
+      </c>
+      <c r="F38">
+        <v>49</v>
+      </c>
+      <c r="G38">
+        <v>593</v>
+      </c>
+      <c r="H38">
+        <v>64</v>
+      </c>
+      <c r="I38">
+        <v>0.1750671887785336</v>
+      </c>
+      <c r="J38">
+        <v>0.08838989885811938</v>
+      </c>
+      <c r="K38">
+        <v>0.2177591592514952</v>
+      </c>
+      <c r="L38">
+        <v>0.08388999452183939</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39">
+        <v>64</v>
+      </c>
+      <c r="F39">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>593</v>
+      </c>
+      <c r="H39">
+        <v>64</v>
+      </c>
+      <c r="I39">
+        <v>0.4300037401795317</v>
+      </c>
+      <c r="J39">
+        <v>2.848084359241216E-05</v>
+      </c>
+      <c r="K39">
+        <v>0.5230983980371547</v>
+      </c>
+      <c r="L39">
+        <v>9.221065908870596E-06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>64</v>
+      </c>
+      <c r="F40">
+        <v>49</v>
+      </c>
+      <c r="G40">
+        <v>593</v>
+      </c>
+      <c r="H40">
+        <v>64</v>
+      </c>
+      <c r="I40">
+        <v>0.1847483236418626</v>
+      </c>
+      <c r="J40">
+        <v>0.07214838607881284</v>
+      </c>
+      <c r="K40">
+        <v>0.2337840554714518</v>
+      </c>
+      <c r="L40">
+        <v>0.06298932587771883</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <v>64</v>
+      </c>
+      <c r="F41">
+        <v>49</v>
+      </c>
+      <c r="G41">
+        <v>593</v>
+      </c>
+      <c r="H41">
+        <v>64</v>
+      </c>
+      <c r="I41">
+        <v>0.4251631727478672</v>
+      </c>
+      <c r="J41">
+        <v>3.500851550453472E-05</v>
+      </c>
+      <c r="K41">
+        <v>0.5206235105900572</v>
+      </c>
+      <c r="L41">
+        <v>1.033794207757365E-05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="51">
   <si>
     <t>metric</t>
   </si>
@@ -1657,6 +1657,9 @@
       <c r="C30" t="s">
         <v>48</v>
       </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
       <c r="E30">
         <v>64</v>
       </c>
@@ -1692,6 +1695,9 @@
       <c r="C31" t="s">
         <v>48</v>
       </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
       <c r="E31">
         <v>64</v>
       </c>
@@ -1727,6 +1733,9 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
       <c r="E32">
         <v>64</v>
       </c>
@@ -1762,6 +1771,9 @@
       <c r="C33" t="s">
         <v>48</v>
       </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
       <c r="E33">
         <v>64</v>
       </c>
@@ -1797,6 +1809,9 @@
       <c r="C34" t="s">
         <v>48</v>
       </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
       <c r="E34">
         <v>64</v>
       </c>
@@ -1832,6 +1847,9 @@
       <c r="C35" t="s">
         <v>48</v>
       </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
       <c r="E35">
         <v>64</v>
       </c>
@@ -1867,6 +1885,9 @@
       <c r="C36" t="s">
         <v>48</v>
       </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
       <c r="E36">
         <v>64</v>
       </c>
@@ -1902,6 +1923,9 @@
       <c r="C37" t="s">
         <v>48</v>
       </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
       <c r="E37">
         <v>64</v>
       </c>
@@ -1937,6 +1961,9 @@
       <c r="C38" t="s">
         <v>48</v>
       </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
       <c r="E38">
         <v>64</v>
       </c>
@@ -1972,6 +1999,9 @@
       <c r="C39" t="s">
         <v>48</v>
       </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
       <c r="E39">
         <v>64</v>
       </c>
@@ -2007,6 +2037,9 @@
       <c r="C40" t="s">
         <v>48</v>
       </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
       <c r="E40">
         <v>64</v>
       </c>
@@ -2042,6 +2075,9 @@
       <c r="C41" t="s">
         <v>48</v>
       </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
       <c r="E41">
         <v>64</v>
       </c>
@@ -2076,6 +2112,9 @@
       </c>
       <c r="C42" t="s">
         <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -3178,6 +3217,9 @@
       <c r="C30" t="s">
         <v>48</v>
       </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
       <c r="E30">
         <v>64</v>
       </c>
@@ -3213,6 +3255,9 @@
       <c r="C31" t="s">
         <v>48</v>
       </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
       <c r="E31">
         <v>64</v>
       </c>
@@ -3248,6 +3293,9 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
       <c r="E32">
         <v>64</v>
       </c>
@@ -3283,6 +3331,9 @@
       <c r="C33" t="s">
         <v>48</v>
       </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
       <c r="E33">
         <v>64</v>
       </c>
@@ -3318,6 +3369,9 @@
       <c r="C34" t="s">
         <v>48</v>
       </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
       <c r="E34">
         <v>64</v>
       </c>
@@ -3353,6 +3407,9 @@
       <c r="C35" t="s">
         <v>48</v>
       </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
       <c r="E35">
         <v>64</v>
       </c>
@@ -3388,6 +3445,9 @@
       <c r="C36" t="s">
         <v>48</v>
       </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
       <c r="E36">
         <v>64</v>
       </c>
@@ -3423,6 +3483,9 @@
       <c r="C37" t="s">
         <v>48</v>
       </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
       <c r="E37">
         <v>64</v>
       </c>
@@ -3458,6 +3521,9 @@
       <c r="C38" t="s">
         <v>48</v>
       </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
       <c r="E38">
         <v>64</v>
       </c>
@@ -3493,6 +3559,9 @@
       <c r="C39" t="s">
         <v>48</v>
       </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
       <c r="E39">
         <v>64</v>
       </c>
@@ -3528,6 +3597,9 @@
       <c r="C40" t="s">
         <v>48</v>
       </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
       <c r="E40">
         <v>64</v>
       </c>
@@ -3563,6 +3635,9 @@
       <c r="C41" t="s">
         <v>48</v>
       </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
       <c r="E41">
         <v>64</v>
       </c>
@@ -3597,6 +3672,9 @@
       </c>
       <c r="C42" t="s">
         <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -4747,6 +4825,9 @@
       <c r="C30" t="s">
         <v>48</v>
       </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
       <c r="E30">
         <v>64</v>
       </c>
@@ -4782,6 +4863,9 @@
       <c r="C31" t="s">
         <v>48</v>
       </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
       <c r="E31">
         <v>64</v>
       </c>
@@ -4817,6 +4901,9 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
       <c r="E32">
         <v>64</v>
       </c>
@@ -4852,6 +4939,9 @@
       <c r="C33" t="s">
         <v>48</v>
       </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
       <c r="E33">
         <v>64</v>
       </c>
@@ -4887,6 +4977,9 @@
       <c r="C34" t="s">
         <v>48</v>
       </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
       <c r="E34">
         <v>64</v>
       </c>
@@ -4922,6 +5015,9 @@
       <c r="C35" t="s">
         <v>48</v>
       </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
       <c r="E35">
         <v>64</v>
       </c>
@@ -4957,6 +5053,9 @@
       <c r="C36" t="s">
         <v>48</v>
       </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
       <c r="E36">
         <v>64</v>
       </c>
@@ -4992,6 +5091,9 @@
       <c r="C37" t="s">
         <v>48</v>
       </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
       <c r="E37">
         <v>64</v>
       </c>
@@ -5027,6 +5129,9 @@
       <c r="C38" t="s">
         <v>48</v>
       </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
       <c r="E38">
         <v>64</v>
       </c>
@@ -5062,6 +5167,9 @@
       <c r="C39" t="s">
         <v>48</v>
       </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
       <c r="E39">
         <v>64</v>
       </c>
@@ -5097,6 +5205,9 @@
       <c r="C40" t="s">
         <v>48</v>
       </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
       <c r="E40">
         <v>64</v>
       </c>
@@ -5132,6 +5243,9 @@
       <c r="C41" t="s">
         <v>48</v>
       </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
       <c r="E41">
         <v>64</v>
       </c>
@@ -5166,6 +5280,9 @@
       </c>
       <c r="C42" t="s">
         <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -6076,6 +6193,9 @@
       <c r="C30" t="s">
         <v>48</v>
       </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
       <c r="E30">
         <v>64</v>
       </c>
@@ -6111,6 +6231,9 @@
       <c r="C31" t="s">
         <v>48</v>
       </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
       <c r="E31">
         <v>64</v>
       </c>
@@ -6146,6 +6269,9 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
       <c r="E32">
         <v>64</v>
       </c>
@@ -6181,6 +6307,9 @@
       <c r="C33" t="s">
         <v>48</v>
       </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
       <c r="E33">
         <v>64</v>
       </c>
@@ -6216,6 +6345,9 @@
       <c r="C34" t="s">
         <v>48</v>
       </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
       <c r="E34">
         <v>64</v>
       </c>
@@ -6251,6 +6383,9 @@
       <c r="C35" t="s">
         <v>48</v>
       </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
       <c r="E35">
         <v>64</v>
       </c>
@@ -6286,6 +6421,9 @@
       <c r="C36" t="s">
         <v>48</v>
       </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
       <c r="E36">
         <v>64</v>
       </c>
@@ -6321,6 +6459,9 @@
       <c r="C37" t="s">
         <v>48</v>
       </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
       <c r="E37">
         <v>64</v>
       </c>
@@ -6356,6 +6497,9 @@
       <c r="C38" t="s">
         <v>48</v>
       </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
       <c r="E38">
         <v>64</v>
       </c>
@@ -6391,6 +6535,9 @@
       <c r="C39" t="s">
         <v>48</v>
       </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
       <c r="E39">
         <v>64</v>
       </c>
@@ -6426,6 +6573,9 @@
       <c r="C40" t="s">
         <v>48</v>
       </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
       <c r="E40">
         <v>64</v>
       </c>
@@ -6461,6 +6611,9 @@
       <c r="C41" t="s">
         <v>48</v>
       </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
       <c r="E41">
         <v>64</v>
       </c>
@@ -6495,6 +6648,9 @@
       </c>
       <c r="C42" t="s">
         <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -7645,6 +7801,9 @@
       <c r="C30" t="s">
         <v>48</v>
       </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
       <c r="E30">
         <v>64</v>
       </c>
@@ -7680,6 +7839,9 @@
       <c r="C31" t="s">
         <v>48</v>
       </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
       <c r="E31">
         <v>64</v>
       </c>
@@ -7715,6 +7877,9 @@
       <c r="C32" t="s">
         <v>48</v>
       </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
       <c r="E32">
         <v>64</v>
       </c>
@@ -7750,6 +7915,9 @@
       <c r="C33" t="s">
         <v>48</v>
       </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
       <c r="E33">
         <v>64</v>
       </c>
@@ -7785,6 +7953,9 @@
       <c r="C34" t="s">
         <v>48</v>
       </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
       <c r="E34">
         <v>64</v>
       </c>
@@ -7820,6 +7991,9 @@
       <c r="C35" t="s">
         <v>48</v>
       </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
       <c r="E35">
         <v>64</v>
       </c>
@@ -7855,6 +8029,9 @@
       <c r="C36" t="s">
         <v>48</v>
       </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
       <c r="E36">
         <v>64</v>
       </c>
@@ -7890,6 +8067,9 @@
       <c r="C37" t="s">
         <v>48</v>
       </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
       <c r="E37">
         <v>64</v>
       </c>
@@ -7925,6 +8105,9 @@
       <c r="C38" t="s">
         <v>48</v>
       </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
       <c r="E38">
         <v>64</v>
       </c>
@@ -7960,6 +8143,9 @@
       <c r="C39" t="s">
         <v>48</v>
       </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
       <c r="E39">
         <v>64</v>
       </c>
@@ -7995,6 +8181,9 @@
       <c r="C40" t="s">
         <v>48</v>
       </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
       <c r="E40">
         <v>64</v>
       </c>
@@ -8030,6 +8219,9 @@
       <c r="C41" t="s">
         <v>48</v>
       </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
       <c r="E41">
         <v>64</v>
       </c>
@@ -8064,6 +8256,9 @@
       </c>
       <c r="C42" t="s">
         <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
       </c>
       <c r="E42">
         <v>8</v>

--- a/data/correlation_analysis.xlsx
+++ b/data/correlation_analysis.xlsx
@@ -1664,25 +1664,25 @@
         <v>64</v>
       </c>
       <c r="F30">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G30">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H30">
         <v>64</v>
       </c>
       <c r="I30">
-        <v>0.3418050362170402</v>
+        <v>0.3534197704574251</v>
       </c>
       <c r="J30">
-        <v>0.001004349555378589</v>
+        <v>0.0006712067605239145</v>
       </c>
       <c r="K30">
-        <v>0.4056114839282338</v>
+        <v>0.4218724281893146</v>
       </c>
       <c r="L30">
-        <v>0.0008838558860104442</v>
+        <v>0.0005164967605085171</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1702,25 +1702,25 @@
         <v>64</v>
       </c>
       <c r="F31">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H31">
         <v>64</v>
       </c>
       <c r="I31">
-        <v>0.279314216373952</v>
+        <v>0.2728746955353595</v>
       </c>
       <c r="J31">
-        <v>0.006440592968704181</v>
+        <v>0.007775816433438667</v>
       </c>
       <c r="K31">
-        <v>0.3562627675046445</v>
+        <v>0.3445389167723131</v>
       </c>
       <c r="L31">
-        <v>0.003859966882439438</v>
+        <v>0.00530510449459072</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1740,25 +1740,25 @@
         <v>64</v>
       </c>
       <c r="F32">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G32">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H32">
         <v>64</v>
       </c>
       <c r="I32">
-        <v>0.3152570722390177</v>
+        <v>0.3301903019766554</v>
       </c>
       <c r="J32">
-        <v>0.002414741112708488</v>
+        <v>0.00148533808206302</v>
       </c>
       <c r="K32">
-        <v>0.3790655710532781</v>
+        <v>0.3959555653824857</v>
       </c>
       <c r="L32">
-        <v>0.002008860935731097</v>
+        <v>0.001200840572111667</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1778,25 +1778,25 @@
         <v>64</v>
       </c>
       <c r="F33">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G33">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H33">
         <v>64</v>
       </c>
       <c r="I33">
-        <v>0.3034624195186741</v>
+        <v>0.2970228986800816</v>
       </c>
       <c r="J33">
-        <v>0.003076304955910668</v>
+        <v>0.003765135973666557</v>
       </c>
       <c r="K33">
-        <v>0.3774523130235019</v>
+        <v>0.3666874052270604</v>
       </c>
       <c r="L33">
-        <v>0.002107109964675385</v>
+        <v>0.00288020938078964</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1816,25 +1816,25 @@
         <v>64</v>
       </c>
       <c r="F34">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G34">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H34">
         <v>64</v>
       </c>
       <c r="I34">
-        <v>0.3645312773432739</v>
+        <v>0.3513653621344875</v>
       </c>
       <c r="J34">
-        <v>0.0004312956077763248</v>
+        <v>0.0006912768452287022</v>
       </c>
       <c r="K34">
-        <v>0.4372373621113425</v>
+        <v>0.4259988561331101</v>
       </c>
       <c r="L34">
-        <v>0.0003031157737914172</v>
+        <v>0.0004487226446072882</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1854,25 +1854,25 @@
         <v>64</v>
       </c>
       <c r="F35">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G35">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H35">
         <v>64</v>
       </c>
       <c r="I35">
-        <v>0.3176259577539492</v>
+        <v>0.3290572261564049</v>
       </c>
       <c r="J35">
-        <v>0.002086286721444307</v>
+        <v>0.001430475268099533</v>
       </c>
       <c r="K35">
-        <v>0.3904345772342148</v>
+        <v>0.3976971715576678</v>
       </c>
       <c r="L35">
-        <v>0.001425026545059507</v>
+        <v>0.0011370265110021</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1892,25 +1892,25 @@
         <v>64</v>
       </c>
       <c r="F36">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G36">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H36">
         <v>64</v>
       </c>
       <c r="I36">
-        <v>0.3612397985410773</v>
+        <v>0.3480738833322909</v>
       </c>
       <c r="J36">
-        <v>0.0004859755544250555</v>
+        <v>0.0007759590617761162</v>
       </c>
       <c r="K36">
-        <v>0.4397104595271652</v>
+        <v>0.4297241547721342</v>
       </c>
       <c r="L36">
-        <v>0.0002775364452370338</v>
+        <v>0.0003945992840144728</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1930,25 +1930,25 @@
         <v>64</v>
       </c>
       <c r="F37">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G37">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H37">
         <v>64</v>
       </c>
       <c r="I37">
-        <v>0.3274241878131969</v>
+        <v>0.3355893795292368</v>
       </c>
       <c r="J37">
-        <v>0.001510770054291855</v>
+        <v>0.001147072973618185</v>
       </c>
       <c r="K37">
-        <v>0.3996920472516634</v>
+        <v>0.4076715500276461</v>
       </c>
       <c r="L37">
-        <v>0.001067701210651935</v>
+        <v>0.0008269258475472268</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1968,10 +1968,10 @@
         <v>64</v>
       </c>
       <c r="F38">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G38">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H38">
         <v>64</v>
@@ -1983,10 +1983,10 @@
         <v>0.06277226494783034</v>
       </c>
       <c r="K38">
-        <v>0.2221963583386178</v>
+        <v>0.2219798228369652</v>
       </c>
       <c r="L38">
-        <v>0.07761946126493192</v>
+        <v>0.07791656080481281</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2006,25 +2006,25 @@
         <v>64</v>
       </c>
       <c r="F39">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G39">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H39">
         <v>64</v>
       </c>
       <c r="I39">
-        <v>0.4177639144036919</v>
+        <v>0.4113243935650994</v>
       </c>
       <c r="J39">
-        <v>4.603037684741663E-05</v>
+        <v>6.017918704588355E-05</v>
       </c>
       <c r="K39">
-        <v>0.5197470712523259</v>
+        <v>0.516313436868978</v>
       </c>
       <c r="L39">
-        <v>1.076278914057353E-05</v>
+        <v>1.258878420384281E-05</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2044,25 +2044,25 @@
         <v>64</v>
       </c>
       <c r="F40">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G40">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H40">
         <v>64</v>
       </c>
       <c r="I40">
-        <v>0.1988202058915451</v>
+        <v>0.2068696069397858</v>
       </c>
       <c r="J40">
-        <v>0.05246287758794487</v>
+        <v>0.04360888927899143</v>
       </c>
       <c r="K40">
-        <v>0.2425816291370515</v>
+        <v>0.2481187512507383</v>
       </c>
       <c r="L40">
-        <v>0.05343862528962646</v>
+        <v>0.04805749138679081</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2082,25 +2082,25 @@
         <v>64</v>
       </c>
       <c r="F41">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G41">
-        <v>963</v>
+        <v>746</v>
       </c>
       <c r="H41">
         <v>64</v>
       </c>
       <c r="I41">
-        <v>0.4161540341940438</v>
+        <v>0.4064947529361549</v>
       </c>
       <c r="J41">
-        <v>4.923775603069727E-05</v>
+        <v>7.339650020479744E-05</v>
       </c>
       <c r="K41">
-        <v>0.5133438071320287</v>
+        <v>0.5055485290725366</v>
       </c>
       <c r="L41">
-        <v>1.439640264622759E-05</v>
+        <v>2.035392474186998E-05</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -3224,7 +3224,7 @@
         <v>64</v>
       </c>
       <c r="F30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>61</v>
@@ -3233,16 +3233,16 @@
         <v>64</v>
       </c>
       <c r="I30">
-        <v>0.2719614374971822</v>
+        <v>0.3904027893196477</v>
       </c>
       <c r="J30">
-        <v>0.01002854427435773</v>
+        <v>0.0002129498242777266</v>
       </c>
       <c r="K30">
-        <v>0.3133954770236209</v>
+        <v>0.460943310071574</v>
       </c>
       <c r="L30">
-        <v>0.01168143094910069</v>
+        <v>0.0001265642816176729</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -3262,7 +3262,7 @@
         <v>64</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G31">
         <v>61</v>
@@ -3271,16 +3271,16 @@
         <v>64</v>
       </c>
       <c r="I31">
-        <v>0.2736099381762394</v>
+        <v>0.2173087272491222</v>
       </c>
       <c r="J31">
-        <v>0.008646828924648913</v>
+        <v>0.03667913753111851</v>
       </c>
       <c r="K31">
-        <v>0.3503163560182605</v>
+        <v>0.2738382762168994</v>
       </c>
       <c r="L31">
-        <v>0.004542269001287748</v>
+        <v>0.02855557097760267</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -3300,7 +3300,7 @@
         <v>64</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G32">
         <v>61</v>
@@ -3309,16 +3309,16 @@
         <v>64</v>
       </c>
       <c r="I32">
-        <v>0.2153788565413926</v>
+        <v>0.3514510370972793</v>
       </c>
       <c r="J32">
-        <v>0.04143627362695777</v>
+        <v>0.0008571043647401488</v>
       </c>
       <c r="K32">
-        <v>0.2572745950545759</v>
+        <v>0.4287937049201984</v>
       </c>
       <c r="L32">
-        <v>0.04013875927915869</v>
+        <v>0.0004075291164306208</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -3338,7 +3338,7 @@
         <v>64</v>
       </c>
       <c r="F33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <v>61</v>
@@ -3347,16 +3347,16 @@
         <v>64</v>
       </c>
       <c r="I33">
-        <v>0.31434151473322</v>
+        <v>0.2447944160711455</v>
       </c>
       <c r="J33">
-        <v>0.002556326771866221</v>
+        <v>0.0185936471931966</v>
       </c>
       <c r="K33">
-        <v>0.3876039941421227</v>
+        <v>0.2985286125971116</v>
       </c>
       <c r="L33">
-        <v>0.001553979051888317</v>
+        <v>0.01657174471669363</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -3376,7 +3376,7 @@
         <v>64</v>
       </c>
       <c r="F34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G34">
         <v>61</v>
@@ -3385,16 +3385,16 @@
         <v>64</v>
       </c>
       <c r="I34">
-        <v>0.3539302241613812</v>
+        <v>0.2923939523370589</v>
       </c>
       <c r="J34">
-        <v>0.000772349952058487</v>
+        <v>0.00538425569427587</v>
       </c>
       <c r="K34">
-        <v>0.424200451879057</v>
+        <v>0.3482345485452505</v>
       </c>
       <c r="L34">
-        <v>0.000477197190019958</v>
+        <v>0.004805173167919696</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -3414,7 +3414,7 @@
         <v>64</v>
       </c>
       <c r="F35">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G35">
         <v>61</v>
@@ -3423,16 +3423,16 @@
         <v>64</v>
       </c>
       <c r="I35">
-        <v>0.2811386444097411</v>
+        <v>0.3633252008766494</v>
       </c>
       <c r="J35">
-        <v>0.007360365207894896</v>
+        <v>0.0005203537316090988</v>
       </c>
       <c r="K35">
-        <v>0.3230085112671829</v>
+        <v>0.4295631818355375</v>
       </c>
       <c r="L35">
-        <v>0.009232404757910088</v>
+        <v>0.0003968091210594844</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -3452,7 +3452,7 @@
         <v>64</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G36">
         <v>61</v>
@@ -3461,16 +3461,16 @@
         <v>64</v>
       </c>
       <c r="I36">
-        <v>0.3340159915998713</v>
+        <v>0.2888817126693464</v>
       </c>
       <c r="J36">
-        <v>0.001507047945669149</v>
+        <v>0.005965580222035621</v>
       </c>
       <c r="K36">
-        <v>0.4072974713242659</v>
+        <v>0.3511315650201968</v>
       </c>
       <c r="L36">
-        <v>0.0008370102382895101</v>
+        <v>0.004442834056999165</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -3490,7 +3490,7 @@
         <v>64</v>
       </c>
       <c r="F37">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G37">
         <v>61</v>
@@ -3499,16 +3499,16 @@
         <v>64</v>
       </c>
       <c r="I37">
-        <v>0.2955099489163094</v>
+        <v>0.3807508699834431</v>
       </c>
       <c r="J37">
-        <v>0.004846165788434817</v>
+        <v>0.0002763853901437227</v>
       </c>
       <c r="K37">
-        <v>0.3392314510102669</v>
+        <v>0.444379096233833</v>
       </c>
       <c r="L37">
-        <v>0.006103124812987851</v>
+        <v>0.0002345528805891897</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -3528,7 +3528,7 @@
         <v>64</v>
       </c>
       <c r="F38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G38">
         <v>61</v>
@@ -3537,16 +3537,16 @@
         <v>64</v>
       </c>
       <c r="I38">
-        <v>0.1726664658393744</v>
+        <v>0.1485945051940638</v>
       </c>
       <c r="J38">
-        <v>0.09751909882925842</v>
+        <v>0.1531008710770661</v>
       </c>
       <c r="K38">
-        <v>0.2181695020568528</v>
+        <v>0.1703600680147187</v>
       </c>
       <c r="L38">
-        <v>0.08329383026399091</v>
+        <v>0.1783408232311354</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -3566,7 +3566,7 @@
         <v>64</v>
       </c>
       <c r="F39">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G39">
         <v>61</v>
@@ -3575,16 +3575,16 @@
         <v>64</v>
       </c>
       <c r="I39">
-        <v>0.362156843734893</v>
+        <v>0.4062728379005328</v>
       </c>
       <c r="J39">
-        <v>0.0005099871944660304</v>
+        <v>9.379164415469421E-05</v>
       </c>
       <c r="K39">
-        <v>0.4336277844655613</v>
+        <v>0.4981657593235443</v>
       </c>
       <c r="L39">
-        <v>0.0003443273285276675</v>
+        <v>2.803715666855235E-05</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -3604,7 +3604,7 @@
         <v>64</v>
       </c>
       <c r="F40">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G40">
         <v>61</v>
@@ -3613,16 +3613,16 @@
         <v>64</v>
       </c>
       <c r="I40">
-        <v>0.1903758469511051</v>
+        <v>0.182951616221593</v>
       </c>
       <c r="J40">
-        <v>0.06770717172115204</v>
+        <v>0.0785790781774844</v>
       </c>
       <c r="K40">
-        <v>0.2372484551363874</v>
+        <v>0.2159347205426203</v>
       </c>
       <c r="L40">
-        <v>0.05907598619468462</v>
+        <v>0.08658152461048273</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -3642,7 +3642,7 @@
         <v>64</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G41">
         <v>61</v>
@@ -3651,16 +3651,16 @@
         <v>64</v>
       </c>
       <c r="I41">
-        <v>0.3568440294013737</v>
+        <v>0.3839407157326388</v>
       </c>
       <c r="J41">
-        <v>0.0006159986891418091</v>
+        <v>0.0002230203245956442</v>
       </c>
       <c r="K41">
-        <v>0.4270673023540021</v>
+        <v>0.4688236204369153</v>
       </c>
       <c r="L41">
-        <v>0.0004325469834795152</v>
+        <v>9.331672782261764E-05</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -4832,25 +4832,25 @@
         <v>64</v>
       </c>
       <c r="F30">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G30">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H30">
         <v>64</v>
       </c>
       <c r="I30">
-        <v>0.3312066789974757</v>
+        <v>0.3382293788278602</v>
       </c>
       <c r="J30">
-        <v>0.001444545715640912</v>
+        <v>0.001155515231065945</v>
       </c>
       <c r="K30">
-        <v>0.3951613500511048</v>
+        <v>0.3973473501013425</v>
       </c>
       <c r="L30">
-        <v>0.001230998474304181</v>
+        <v>0.001149593318906413</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -4870,25 +4870,25 @@
         <v>64</v>
       </c>
       <c r="F31">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G31">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H31">
         <v>64</v>
       </c>
       <c r="I31">
-        <v>0.2851095580779748</v>
+        <v>0.2805940692071166</v>
       </c>
       <c r="J31">
-        <v>0.005444291726857445</v>
+        <v>0.006284924474363482</v>
       </c>
       <c r="K31">
-        <v>0.3585898901910007</v>
+        <v>0.3566242196106007</v>
       </c>
       <c r="L31">
-        <v>0.003618737360339382</v>
+        <v>0.003821588335446995</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -4908,25 +4908,25 @@
         <v>64</v>
       </c>
       <c r="F32">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G32">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H32">
         <v>64</v>
       </c>
       <c r="I32">
-        <v>0.298003001904997</v>
+        <v>0.3000019797465787</v>
       </c>
       <c r="J32">
-        <v>0.004153780499267119</v>
+        <v>0.003947108933194522</v>
       </c>
       <c r="K32">
-        <v>0.3693068803776852</v>
+        <v>0.3676544232463521</v>
       </c>
       <c r="L32">
-        <v>0.002671858328610249</v>
+        <v>0.002801666638565392</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -4946,25 +4946,25 @@
         <v>64</v>
       </c>
       <c r="F33">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G33">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H33">
         <v>64</v>
       </c>
       <c r="I33">
-        <v>0.3092713850337354</v>
+        <v>0.3015579939179931</v>
       </c>
       <c r="J33">
-        <v>0.002569376231396744</v>
+        <v>0.003317371415491002</v>
       </c>
       <c r="K33">
-        <v>0.3769339037247535</v>
+        <v>0.376206378789427</v>
       </c>
       <c r="L33">
-        <v>0.002139581888614954</v>
+        <v>0.002185907028681405</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -4984,25 +4984,25 @@
         <v>64</v>
       </c>
       <c r="F34">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G34">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H34">
         <v>64</v>
       </c>
       <c r="I34">
-        <v>0.3606202670394066</v>
+        <v>0.3725676851031911</v>
       </c>
       <c r="J34">
-        <v>0.0005004520767949459</v>
+        <v>0.0003282116204522614</v>
       </c>
       <c r="K34">
-        <v>0.4411592251170234</v>
+        <v>0.4500678518231889</v>
       </c>
       <c r="L34">
-        <v>0.000263484125366215</v>
+        <v>0.0001904415167932243</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -5022,25 +5022,25 @@
         <v>64</v>
       </c>
       <c r="F35">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G35">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H35">
         <v>64</v>
       </c>
       <c r="I35">
-        <v>0.3022825375654209</v>
+        <v>0.3058959069237767</v>
       </c>
       <c r="J35">
-        <v>0.003417872613560628</v>
+        <v>0.003084159237988771</v>
       </c>
       <c r="K35">
-        <v>0.3773506763775762</v>
+        <v>0.3795788161572406</v>
       </c>
       <c r="L35">
-        <v>0.002113441279970249</v>
+        <v>0.001978475130175069</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -5060,25 +5060,25 @@
         <v>64</v>
       </c>
       <c r="F36">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G36">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H36">
         <v>64</v>
       </c>
       <c r="I36">
-        <v>0.363913602811456</v>
+        <v>0.3758647442633963</v>
       </c>
       <c r="J36">
-        <v>0.0004442465007961315</v>
+        <v>0.0002903756001085439</v>
       </c>
       <c r="K36">
-        <v>0.4439454280006037</v>
+        <v>0.4513827412066456</v>
       </c>
       <c r="L36">
-        <v>0.0002382722252024225</v>
+        <v>0.0001813935716320079</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -5098,25 +5098,25 @@
         <v>64</v>
       </c>
       <c r="F37">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G37">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H37">
         <v>64</v>
       </c>
       <c r="I37">
-        <v>0.3088183762154841</v>
+        <v>0.3140749418682626</v>
       </c>
       <c r="J37">
-        <v>0.002783248451265792</v>
+        <v>0.002378802479019535</v>
       </c>
       <c r="K37">
-        <v>0.38679535297946</v>
+        <v>0.3899278485103821</v>
       </c>
       <c r="L37">
-        <v>0.001592694770480384</v>
+        <v>0.001447379238525057</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -5136,25 +5136,25 @@
         <v>64</v>
       </c>
       <c r="F38">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G38">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H38">
         <v>64</v>
       </c>
       <c r="I38">
-        <v>0.2029593464283888</v>
+        <v>0.1838374936184557</v>
       </c>
       <c r="J38">
-        <v>0.0478581302625294</v>
+        <v>0.07340879911871581</v>
       </c>
       <c r="K38">
-        <v>0.2294084390662924</v>
+        <v>0.2211886858271855</v>
       </c>
       <c r="L38">
-        <v>0.0682278542017089</v>
+        <v>0.07900973425176479</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -5174,25 +5174,25 @@
         <v>64</v>
       </c>
       <c r="F39">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G39">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H39">
         <v>64</v>
       </c>
       <c r="I39">
-        <v>0.3962539620744734</v>
+        <v>0.4160532750312418</v>
       </c>
       <c r="J39">
-        <v>0.000111988463487014</v>
+        <v>5.084947095560188E-05</v>
       </c>
       <c r="K39">
-        <v>0.5058369465496242</v>
+        <v>0.5153232347565394</v>
       </c>
       <c r="L39">
-        <v>2.00978250431268E-05</v>
+        <v>1.316661746779531E-05</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -5212,25 +5212,25 @@
         <v>64</v>
       </c>
       <c r="F40">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G40">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H40">
         <v>64</v>
       </c>
       <c r="I40">
-        <v>0.2174564426018452</v>
+        <v>0.1999635895498992</v>
       </c>
       <c r="J40">
-        <v>0.034009720061427</v>
+        <v>0.05149604038277988</v>
       </c>
       <c r="K40">
-        <v>0.2521760511419114</v>
+        <v>0.2459989412164726</v>
       </c>
       <c r="L40">
-        <v>0.04440330791153663</v>
+        <v>0.05006258942290791</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -5250,25 +5250,25 @@
         <v>64</v>
       </c>
       <c r="F41">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G41">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H41">
         <v>64</v>
       </c>
       <c r="I41">
-        <v>0.3946431736107561</v>
+        <v>0.4128280558449531</v>
       </c>
       <c r="J41">
-        <v>0.0001194128933263328</v>
+        <v>5.812914902489906E-05</v>
       </c>
       <c r="K41">
-        <v>0.4992788843756686</v>
+        <v>0.5070015904925516</v>
       </c>
       <c r="L41">
-        <v>2.67281327133127E-05</v>
+        <v>1.909381654421383E-05</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -7808,25 +7808,25 @@
         <v>64</v>
       </c>
       <c r="F30">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G30">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H30">
         <v>64</v>
       </c>
       <c r="I30">
-        <v>0.3276113363986184</v>
+        <v>0.3755551470662721</v>
       </c>
       <c r="J30">
-        <v>0.001655631257960234</v>
+        <v>0.0003208366098090241</v>
       </c>
       <c r="K30">
-        <v>0.3991009701707551</v>
+        <v>0.4500026854966419</v>
       </c>
       <c r="L30">
-        <v>0.001087833473222033</v>
+        <v>0.0001909005142370093</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -7846,25 +7846,25 @@
         <v>64</v>
       </c>
       <c r="F31">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G31">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H31">
         <v>64</v>
       </c>
       <c r="I31">
-        <v>0.3025354644790327</v>
+        <v>0.2600357232115845</v>
       </c>
       <c r="J31">
-        <v>0.003233526189215585</v>
+        <v>0.01156830161334135</v>
       </c>
       <c r="K31">
-        <v>0.3718518389264061</v>
+        <v>0.3224143226622697</v>
       </c>
       <c r="L31">
-        <v>0.002482411365845201</v>
+        <v>0.009369643674346645</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -7884,25 +7884,25 @@
         <v>64</v>
       </c>
       <c r="F32">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G32">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H32">
         <v>64</v>
       </c>
       <c r="I32">
-        <v>0.3093183176149393</v>
+        <v>0.3618985962638622</v>
       </c>
       <c r="J32">
-        <v>0.0029754480217311</v>
+        <v>0.0005262309242521557</v>
       </c>
       <c r="K32">
-        <v>0.3779946688636478</v>
+        <v>0.4291614730760027</v>
       </c>
       <c r="L32">
-        <v>0.002073610609920638</v>
+        <v>0.0004023730533292708</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -7922,25 +7922,25 @@
         <v>64</v>
       </c>
       <c r="F33">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G33">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H33">
         <v>64</v>
       </c>
       <c r="I33">
-        <v>0.3235112566829123</v>
+        <v>0.2848799005884874</v>
       </c>
       <c r="J33">
-        <v>0.001639540198139356</v>
+        <v>0.005669759103688426</v>
       </c>
       <c r="K33">
-        <v>0.3928883822267352</v>
+        <v>0.3466500460421101</v>
       </c>
       <c r="L33">
-        <v>0.001321114481430784</v>
+        <v>0.005014185640860448</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -7960,25 +7960,25 @@
         <v>64</v>
       </c>
       <c r="F34">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G34">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H34">
         <v>64</v>
       </c>
       <c r="I34">
-        <v>0.3604076213996629</v>
+        <v>0.3217025240710855</v>
       </c>
       <c r="J34">
-        <v>0.0005149830017394812</v>
+        <v>0.001983922422328447</v>
       </c>
       <c r="K34">
-        <v>0.4338907809518547</v>
+        <v>0.3936133951297886</v>
       </c>
       <c r="L34">
-        <v>0.0003411602703865751</v>
+        <v>0.001291745333408583</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -7998,25 +7998,25 @@
         <v>64</v>
       </c>
       <c r="F35">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G35">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H35">
         <v>64</v>
       </c>
       <c r="I35">
-        <v>0.318344569436641</v>
+        <v>0.3242600845134231</v>
       </c>
       <c r="J35">
-        <v>0.002084025119649695</v>
+        <v>0.001760896484248526</v>
       </c>
       <c r="K35">
-        <v>0.386943018934536</v>
+        <v>0.4020661562064903</v>
       </c>
       <c r="L35">
-        <v>0.001585560908767367</v>
+        <v>0.0009901813688402113</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -8036,25 +8036,25 @@
         <v>64</v>
       </c>
       <c r="F36">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G36">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H36">
         <v>64</v>
       </c>
       <c r="I36">
-        <v>0.3604076213996629</v>
+        <v>0.32678203760905</v>
       </c>
       <c r="J36">
-        <v>0.0005149830017394812</v>
+        <v>0.001681080018936784</v>
       </c>
       <c r="K36">
-        <v>0.438023372270539</v>
+        <v>0.3989034668245361</v>
       </c>
       <c r="L36">
-        <v>0.0002947617347795054</v>
+        <v>0.001094636433219306</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -8074,25 +8074,25 @@
         <v>64</v>
       </c>
       <c r="F37">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G37">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H37">
         <v>64</v>
       </c>
       <c r="I37">
-        <v>0.3281649674655348</v>
+        <v>0.3343407089024414</v>
       </c>
       <c r="J37">
-        <v>0.001509037284530193</v>
+        <v>0.001259332900211386</v>
       </c>
       <c r="K37">
-        <v>0.3974792906174389</v>
+        <v>0.4125367952883267</v>
       </c>
       <c r="L37">
-        <v>0.001144838922675296</v>
+        <v>0.0007054145863726739</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -8112,25 +8112,25 @@
         <v>64</v>
       </c>
       <c r="F38">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G38">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H38">
         <v>64</v>
       </c>
       <c r="I38">
-        <v>0.1750671887785336</v>
+        <v>0.1821906340972885</v>
       </c>
       <c r="J38">
-        <v>0.08838989885811938</v>
+        <v>0.07687038298750423</v>
       </c>
       <c r="K38">
-        <v>0.2177591592514952</v>
+        <v>0.2060828504390355</v>
       </c>
       <c r="L38">
-        <v>0.08388999452183939</v>
+        <v>0.1023095795592537</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -8150,25 +8150,25 @@
         <v>64</v>
       </c>
       <c r="F39">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G39">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H39">
         <v>64</v>
       </c>
       <c r="I39">
-        <v>0.4300037401795317</v>
+        <v>0.3958505595386541</v>
       </c>
       <c r="J39">
-        <v>2.848084359241216E-05</v>
+        <v>0.0001211139011181233</v>
       </c>
       <c r="K39">
-        <v>0.5230983980371547</v>
+        <v>0.4967848082604943</v>
       </c>
       <c r="L39">
-        <v>9.221065908870596E-06</v>
+        <v>2.974373219042705E-05</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -8188,25 +8188,25 @@
         <v>64</v>
       </c>
       <c r="F40">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G40">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H40">
         <v>64</v>
       </c>
       <c r="I40">
-        <v>0.1847483236418626</v>
+        <v>0.1987534190152238</v>
       </c>
       <c r="J40">
-        <v>0.07214838607881284</v>
+        <v>0.05361033614525734</v>
       </c>
       <c r="K40">
-        <v>0.2337840554714518</v>
+        <v>0.2318075659742387</v>
       </c>
       <c r="L40">
-        <v>0.06298932587771883</v>
+        <v>0.06531395240616776</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -8226,25 +8226,25 @@
         <v>64</v>
       </c>
       <c r="F41">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G41">
-        <v>593</v>
+        <v>379</v>
       </c>
       <c r="H41">
         <v>64</v>
       </c>
       <c r="I41">
-        <v>0.4251631727478672</v>
+        <v>0.3875691670796865</v>
       </c>
       <c r="J41">
-        <v>3.500851550453472E-05</v>
+        <v>0.0001675886356837726</v>
       </c>
       <c r="K41">
-        <v>0.5206235105900572</v>
+        <v>0.4854431233324121</v>
       </c>
       <c r="L41">
-        <v>1.033794207757365E-05</v>
+        <v>4.786569996383044E-05</v>
       </c>
     </row>
     <row r="42" spans="1:12">
